--- a/LibraryHub_Test_Case_Matrix.xlsx
+++ b/LibraryHub_Test_Case_Matrix.xlsx
@@ -7,7 +7,7 @@
     <sheet name="Test Cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Test Cases'!A1:K112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1">'Test Cases'!A1:K133</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -420,7 +420,7 @@
         <v>Total Test Cases</v>
       </c>
       <c r="B2">
-        <v>111</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
@@ -444,7 +444,7 @@
         <v>High</v>
       </c>
       <c r="B5">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Medium</v>
       </c>
       <c r="B6">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -460,7 +460,7 @@
         <v>Low</v>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -484,7 +484,7 @@
         <v>Login</v>
       </c>
       <c r="B10">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -492,7 +492,7 @@
         <v>Navigation &amp; UI</v>
       </c>
       <c r="B11">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -500,7 +500,7 @@
         <v>Dashboard</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -540,7 +540,7 @@
         <v>Issue Book</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -572,7 +572,7 @@
         <v>Categories</v>
       </c>
       <c r="B21">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -585,15 +585,15 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v/>
-      </c>
-      <c r="B23" t="str">
-        <v/>
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="B23">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>By Automation Status</v>
+        <v/>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -601,22 +601,30 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="B25">
-        <v>111</v>
+        <v>By Automation Status</v>
+      </c>
+      <c r="B25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="B26">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B26"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K133"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1035,33 +1043,35 @@
         <v/>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
-        <v>TC-NAV-001</v>
+        <v>TC-LOGIN-011</v>
       </c>
       <c r="B12" t="str">
-        <v>Navigation &amp; UI</v>
+        <v>Login</v>
       </c>
       <c r="C12" t="str">
-        <v>Sidebar renders all navigation links for an authenticated user</v>
+        <v>Successful login as the seeded Member test account redirects to My Account</v>
       </c>
       <c r="D12" t="str">
-        <v>Medium</v>
+        <v>High</v>
       </c>
       <c r="E12" t="str">
-        <v>User is logged in and on any protected page.</v>
-      </c>
-      <c r="F12" t="str">
-        <v>1. Observe the sidebar</v>
+        <v>User is on the Login page.</v>
+      </c>
+      <c r="F12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter member@library.com
+2. Enter Member@123
+3. Click Login</v>
       </c>
       <c r="G12" t="str">
-        <v>N/A</v>
+        <v>member@library.com / Member@123</v>
       </c>
       <c r="H12" t="str">
-        <v>All nine nav links are visible: Dashboard, Books, Members, Issue Book, Return Books, Overdue Books, Issue History, Categories, Profile.</v>
+        <v>User is redirected to /my-account (not /dashboard); sidebar shows only "My Account" and "Profile".</v>
       </c>
       <c r="I12" t="str">
-        <v>sidebar, nav-dashboard, nav-books, nav-members, nav-issue-book, nav-return-books, nav-overdue-books, nav-issue-history, nav-categories, nav-profile</v>
+        <v>login-form, login-username, login-password, login-button</v>
       </c>
       <c r="J12" t="str">
         <v>Not Automated</v>
@@ -1072,209 +1082,213 @@
     </row>
     <row r="13" xml:space="preserve">
       <c r="A13" t="str">
+        <v>TC-LOGIN-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Login</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Any registered member can log in with their own email and the shared demo password</v>
+      </c>
+      <c r="D13" t="str">
+        <v>High</v>
+      </c>
+      <c r="E13" t="str">
+        <v>A member record exists (e.g. seeded member "Isha Verma").</v>
+      </c>
+      <c r="F13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter that member's own email, e.g. isha.verma@mail.com
+2. Enter Member@123
+3. Click Login</v>
+      </c>
+      <c r="G13" t="str">
+        <v>isha.verma@mail.com / Member@123</v>
+      </c>
+      <c r="H13" t="str">
+        <v>Login succeeds even though this member has no dedicated staff-configured account; user is redirected to /my-account showing that member's own name and data.</v>
+      </c>
+      <c r="I13" t="str">
+        <v>login-username, login-password, login-button</v>
+      </c>
+      <c r="J13" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC-LOGIN-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Login</v>
+      </c>
+      <c r="C14" t="str">
+        <v>A registered member's email fails login with the wrong password</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E14" t="str">
+        <v>A member record exists.</v>
+      </c>
+      <c r="F14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Enter a real member email
+2. Enter an incorrect password
+3. Click Login</v>
+      </c>
+      <c r="G14" t="str">
+        <v>isha.verma@mail.com / WrongPass1!</v>
+      </c>
+      <c r="H14" t="str">
+        <v>Login is rejected with "Incorrect password. Please try again."; user remains on /login.</v>
+      </c>
+      <c r="I14" t="str">
+        <v>login-username, login-password, login-button, login-error</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TC-LOGIN-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Login</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Member login is redirected to /my-account, not /dashboard, when already authenticated</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E15" t="str">
+        <v>A member session is already active.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>1. While logged in as any member, navigate directly to /login</v>
+      </c>
+      <c r="G15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H15" t="str">
+        <v>App immediately redirects to /my-account instead of /dashboard.</v>
+      </c>
+      <c r="I15" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TC-NAV-001</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Sidebar renders all navigation links for an authenticated user</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E16" t="str">
+        <v>User is logged in and on any protected page.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1. Observe the sidebar</v>
+      </c>
+      <c r="G16" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H16" t="str">
+        <v>All nine nav links are visible: Dashboard, Books, Members, Issue Book, Return Books, Overdue Books, Issue History, Categories, Profile.</v>
+      </c>
+      <c r="I16" t="str">
+        <v>sidebar, nav-dashboard, nav-books, nav-members, nav-issue-book, nav-return-books, nav-overdue-books, nav-issue-history, nav-categories, nav-profile</v>
+      </c>
+      <c r="J16" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
         <v>TC-NAV-002</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B17" t="str">
         <v>Navigation &amp; UI</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C17" t="str">
         <v>Each sidebar link navigates to its corresponding route</v>
       </c>
-      <c r="D13" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E13" t="str">
+      <c r="D17" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E17" t="str">
         <v>User is logged in.</v>
       </c>
-      <c r="F13" t="str" xml:space="preserve">
+      <c r="F17" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click each sidebar nav link in turn
 2. Verify the URL and page heading after each click</v>
       </c>
-      <c r="G13" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H13" t="str">
+      <c r="G17" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H17" t="str">
         <v>Each click routes to the matching URL (e.g. nav-books -&gt; /books) and renders that page's content.</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I17" t="str">
         <v>nav-dashboard, nav-books, nav-members, nav-issue-book, nav-return-books, nav-overdue-books, nav-issue-history, nav-categories, nav-profile</v>
       </c>
-      <c r="J13" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+      <c r="J17" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
         <v>TC-NAV-003</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B18" t="str">
         <v>Navigation &amp; UI</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C18" t="str">
         <v>Hamburger menu toggles the mobile sidebar</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D18" t="str">
         <v>Low</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E18" t="str">
         <v>Viewport is narrow (mobile width) and user is logged in.</v>
       </c>
-      <c r="F14" t="str" xml:space="preserve">
+      <c r="F18" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click the hamburger menu icon
 2. Observe the sidebar
 3. Click the scrim/overlay</v>
       </c>
-      <c r="G14" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H14" t="str">
+      <c r="G18" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H18" t="str">
         <v>Sidebar slides into view on first click; clicking the scrim closes it again.</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I18" t="str">
         <v>hamburger-menu, sidebar</v>
-      </c>
-      <c r="J14" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>TC-NAV-004</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Navigation &amp; UI</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Logout button opens a confirmation dialog</v>
-      </c>
-      <c r="D15" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E15" t="str">
-        <v>User is logged in.</v>
-      </c>
-      <c r="F15" t="str">
-        <v>1. Click the Logout button</v>
-      </c>
-      <c r="G15" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H15" t="str">
-        <v>A confirmation dialog appears asking the user to confirm logout.</v>
-      </c>
-      <c r="I15" t="str">
-        <v>logout-button, confirm-logout-dialog</v>
-      </c>
-      <c r="J15" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>TC-NAV-005</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Navigation &amp; UI</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Cancelling the logout confirmation keeps the user signed in</v>
-      </c>
-      <c r="D16" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E16" t="str">
-        <v>Logout confirmation dialog is open.</v>
-      </c>
-      <c r="F16" t="str">
-        <v>1. Click Cancel / "Stay signed in"</v>
-      </c>
-      <c r="G16" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H16" t="str">
-        <v>Dialog closes; user remains authenticated on the current page.</v>
-      </c>
-      <c r="I16" t="str">
-        <v>confirm-logout-dialog</v>
-      </c>
-      <c r="J16" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>TC-NAV-006</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Navigation &amp; UI</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Confirming logout signs the user out</v>
-      </c>
-      <c r="D17" t="str">
-        <v>High</v>
-      </c>
-      <c r="E17" t="str">
-        <v>Logout confirmation dialog is open.</v>
-      </c>
-      <c r="F17" t="str">
-        <v>1. Click Confirm / "Log out"</v>
-      </c>
-      <c r="G17" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H17" t="str">
-        <v>User session is cleared; app redirects to /login.</v>
-      </c>
-      <c r="I17" t="str">
-        <v>confirm-logout-dialog</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>TC-NAV-007</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Navigation &amp; UI</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Unauthenticated access to a protected route redirects to Login</v>
-      </c>
-      <c r="D18" t="str">
-        <v>High</v>
-      </c>
-      <c r="E18" t="str">
-        <v>No active session (logged out).</v>
-      </c>
-      <c r="F18" t="str">
-        <v>1. Directly navigate to a protected URL, e.g. /dashboard or /books</v>
-      </c>
-      <c r="G18" t="str">
-        <v>URL = /books</v>
-      </c>
-      <c r="H18" t="str">
-        <v>App redirects to /login instead of rendering the protected page.</v>
-      </c>
-      <c r="I18" t="str">
-        <v>login-form</v>
       </c>
       <c r="J18" t="str">
         <v>Not Automated</v>
@@ -1285,3385 +1299,4137 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>TC-NAV-008</v>
+        <v>TC-NAV-004</v>
       </c>
       <c r="B19" t="str">
         <v>Navigation &amp; UI</v>
       </c>
       <c r="C19" t="str">
+        <v>Logout button opens a confirmation dialog</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E19" t="str">
+        <v>User is logged in.</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1. Click the Logout button</v>
+      </c>
+      <c r="G19" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H19" t="str">
+        <v>A confirmation dialog appears asking the user to confirm logout.</v>
+      </c>
+      <c r="I19" t="str">
+        <v>logout-button, confirm-logout-dialog</v>
+      </c>
+      <c r="J19" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TC-NAV-005</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Cancelling the logout confirmation keeps the user signed in</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Logout confirmation dialog is open.</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1. Click Cancel / "Stay signed in"</v>
+      </c>
+      <c r="G20" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H20" t="str">
+        <v>Dialog closes; user remains authenticated on the current page.</v>
+      </c>
+      <c r="I20" t="str">
+        <v>confirm-logout-dialog</v>
+      </c>
+      <c r="J20" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TC-NAV-006</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Confirming logout signs the user out</v>
+      </c>
+      <c r="D21" t="str">
+        <v>High</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Logout confirmation dialog is open.</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1. Click Confirm / "Log out"</v>
+      </c>
+      <c r="G21" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H21" t="str">
+        <v>User session is cleared; app redirects to /login.</v>
+      </c>
+      <c r="I21" t="str">
+        <v>confirm-logout-dialog</v>
+      </c>
+      <c r="J21" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TC-NAV-007</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Unauthenticated access to a protected route redirects to Login</v>
+      </c>
+      <c r="D22" t="str">
+        <v>High</v>
+      </c>
+      <c r="E22" t="str">
+        <v>No active session (logged out).</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1. Directly navigate to a protected URL, e.g. /dashboard or /books</v>
+      </c>
+      <c r="G22" t="str">
+        <v>URL = /books</v>
+      </c>
+      <c r="H22" t="str">
+        <v>App redirects to /login instead of rendering the protected page.</v>
+      </c>
+      <c r="I22" t="str">
+        <v>login-form</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TC-NAV-008</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C23" t="str">
         <v>Unmatched route shows the 404 Not Found page</v>
       </c>
-      <c r="D19" t="str">
+      <c r="D23" t="str">
         <v>Low</v>
       </c>
-      <c r="E19" t="str">
+      <c r="E23" t="str">
         <v>User is logged in or logged out.</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F23" t="str">
         <v>1. Navigate to an undefined route, e.g. /this-page-does-not-exist</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G23" t="str">
         <v>URL = /nonexistent-route</v>
       </c>
-      <c r="H19" t="str">
+      <c r="H23" t="str">
         <v>A 404 Not Found page renders with a link back to the Dashboard.</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I23" t="str">
         <v>not-found-page</v>
       </c>
-      <c r="J19" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
+      <c r="J23" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TC-NAV-009</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C24" t="str">
+        <v>A Member role sees only "My Account" and "Profile" in the sidebar</v>
+      </c>
+      <c r="D24" t="str">
+        <v>High</v>
+      </c>
+      <c r="E24" t="str">
+        <v>User is logged in with role Member.</v>
+      </c>
+      <c r="F24" t="str">
+        <v>1. Observe the sidebar</v>
+      </c>
+      <c r="G24" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H24" t="str">
+        <v>Only two nav links are visible: My Account and Profile. Dashboard, Books, Members, Issue Book, Return Books, Overdue Books, Issue History, and Categories are all absent.</v>
+      </c>
+      <c r="I24" t="str">
+        <v>sidebar, nav-my-account, nav-profile</v>
+      </c>
+      <c r="J24" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TC-NAV-010</v>
+      </c>
+      <c r="B25" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C25" t="str">
+        <v>A Member role is redirected to /my-account when navigating directly to a staff-only route</v>
+      </c>
+      <c r="D25" t="str">
+        <v>High</v>
+      </c>
+      <c r="E25" t="str">
+        <v>User is logged in with role Member.</v>
+      </c>
+      <c r="F25" t="str">
+        <v>1. Directly navigate to a staff-only URL, e.g. /books, /members, or /dashboard</v>
+      </c>
+      <c r="G25" t="str">
+        <v>URL = /books</v>
+      </c>
+      <c r="H25" t="str">
+        <v>App redirects to /my-account instead of rendering the staff page.</v>
+      </c>
+      <c r="I25" t="str">
+        <v>my-account-page</v>
+      </c>
+      <c r="J25" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TC-NAV-011</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Navigation &amp; UI</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Admin and Librarian roles retain full access to all staff routes</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E26" t="str">
+        <v>User is logged in as Admin or Librarian.</v>
+      </c>
+      <c r="F26" t="str">
+        <v>1. Navigate to each staff route in turn (Dashboard, Books, Members, Issue Book, Return Books, Overdue Books, Issue History, Categories)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H26" t="str">
+        <v>Every staff route renders normally with no redirect to /my-account.</v>
+      </c>
+      <c r="I26" t="str">
+        <v>sidebar</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
         <v>TC-DASH-001</v>
       </c>
-      <c r="B20" t="str">
+      <c r="B27" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C20" t="str">
+      <c r="C27" t="str">
         <v>Dashboard displays the correct total books count</v>
       </c>
-      <c r="D20" t="str">
+      <c r="D27" t="str">
         <v>High</v>
       </c>
-      <c r="E20" t="str">
+      <c r="E27" t="str">
         <v>User is logged in; a known set of books exists in storage.</v>
       </c>
-      <c r="F20" t="str" xml:space="preserve">
+      <c r="F27" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Total Books stat card</v>
       </c>
-      <c r="G20" t="str">
+      <c r="G27" t="str">
         <v>N books seeded</v>
       </c>
-      <c r="H20" t="str">
+      <c r="H27" t="str">
         <v>Stat card value equals the actual number of books in storage.</v>
       </c>
-      <c r="I20" t="str">
+      <c r="I27" t="str">
         <v>stats-grid, stat-total-books</v>
       </c>
-      <c r="J20" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
+      <c r="J27" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
         <v>TC-DASH-002</v>
       </c>
-      <c r="B21" t="str">
+      <c r="B28" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C21" t="str">
+      <c r="C28" t="str">
         <v>Dashboard displays the correct available books count</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D28" t="str">
         <v>High</v>
       </c>
-      <c r="E21" t="str">
+      <c r="E28" t="str">
         <v>Known books with a mix of available/unavailable copies exist.</v>
       </c>
-      <c r="F21" t="str" xml:space="preserve">
+      <c r="F28" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Available Books stat card</v>
       </c>
-      <c r="G21" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H21" t="str">
+      <c r="G28" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H28" t="str">
         <v>Stat card value equals the sum of books with availableCopies &gt; 0 / total available copies.</v>
       </c>
-      <c r="I21" t="str">
+      <c r="I28" t="str">
         <v>stat-available-books</v>
       </c>
-      <c r="J21" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
+      <c r="J28" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
         <v>TC-DASH-003</v>
       </c>
-      <c r="B22" t="str">
+      <c r="B29" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C22" t="str">
+      <c r="C29" t="str">
         <v>Dashboard displays the correct issued books count</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D29" t="str">
         <v>High</v>
       </c>
-      <c r="E22" t="str">
+      <c r="E29" t="str">
         <v>Known issue records exist with status Issued/Overdue.</v>
       </c>
-      <c r="F22" t="str" xml:space="preserve">
+      <c r="F29" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Issued Books stat card</v>
       </c>
-      <c r="G22" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H22" t="str">
+      <c r="G29" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H29" t="str">
         <v>Stat card value equals the count of active (non-returned) issue records.</v>
       </c>
-      <c r="I22" t="str">
+      <c r="I29" t="str">
         <v>stat-issued-books</v>
       </c>
-      <c r="J22" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23" xml:space="preserve">
-      <c r="A23" t="str">
+      <c r="J29" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30" xml:space="preserve">
+      <c r="A30" t="str">
         <v>TC-DASH-004</v>
       </c>
-      <c r="B23" t="str">
+      <c r="B30" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C23" t="str">
+      <c r="C30" t="str">
         <v>Dashboard displays the correct total members count</v>
       </c>
-      <c r="D23" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E23" t="str">
+      <c r="D30" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E30" t="str">
         <v>Known members exist in storage.</v>
       </c>
-      <c r="F23" t="str" xml:space="preserve">
+      <c r="F30" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Total Members stat card</v>
       </c>
-      <c r="G23" t="str">
+      <c r="G30" t="str">
         <v>N members seeded</v>
       </c>
-      <c r="H23" t="str">
+      <c r="H30" t="str">
         <v>Stat card value equals the actual number of members in storage.</v>
       </c>
-      <c r="I23" t="str">
+      <c r="I30" t="str">
         <v>stat-total-members</v>
       </c>
-      <c r="J23" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24" xml:space="preserve">
-      <c r="A24" t="str">
+      <c r="J30" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
         <v>TC-DASH-005</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B31" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C24" t="str">
+      <c r="C31" t="str">
         <v>Dashboard displays the correct overdue books count</v>
       </c>
-      <c r="D24" t="str">
+      <c r="D31" t="str">
         <v>High</v>
       </c>
-      <c r="E24" t="str">
+      <c r="E31" t="str">
         <v>Some issue records have a due date in the past and no return date.</v>
       </c>
-      <c r="F24" t="str" xml:space="preserve">
+      <c r="F31" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Overdue Books stat card</v>
       </c>
-      <c r="G24" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H24" t="str">
+      <c r="G31" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H31" t="str">
         <v>Stat card value equals the count of unreturned issues past their due date; returned issues are excluded.</v>
       </c>
-      <c r="I24" t="str">
+      <c r="I31" t="str">
         <v>stat-overdue-books</v>
       </c>
-      <c r="J24" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25" xml:space="preserve">
-      <c r="A25" t="str">
+      <c r="J31" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32" xml:space="preserve">
+      <c r="A32" t="str">
         <v>TC-DASH-006</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B32" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C32" t="str">
         <v>Dashboard displays the correct due-today count</v>
       </c>
-      <c r="D25" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E25" t="str">
+      <c r="D32" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E32" t="str">
         <v>At least one active issue has a due date of today.</v>
       </c>
-      <c r="F25" t="str" xml:space="preserve">
+      <c r="F32" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Read the Due Today stat card</v>
       </c>
-      <c r="G25" t="str">
+      <c r="G32" t="str">
         <v>One issue with dueDate = today, status Issued</v>
       </c>
-      <c r="H25" t="str">
+      <c r="H32" t="str">
         <v>Stat card value equals the count of active issues due exactly today.</v>
       </c>
-      <c r="I25" t="str">
+      <c r="I32" t="str">
         <v>stat-due-today</v>
       </c>
-      <c r="J25" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
+      <c r="J32" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33" xml:space="preserve">
+      <c r="A33" t="str">
         <v>TC-DASH-007</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B33" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C33" t="str">
         <v>Recent activity feed lists the latest actions</v>
       </c>
-      <c r="D26" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E26" t="str">
+      <c r="D33" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E33" t="str">
         <v>At least one activity item exists (issue/return/member/book action).</v>
       </c>
-      <c r="F26" t="str" xml:space="preserve">
+      <c r="F33" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Observe the Recent Activity panel</v>
       </c>
-      <c r="G26" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H26" t="str">
+      <c r="G33" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H33" t="str">
         <v>Activity items render with correct message text, ordered most-recent first.</v>
       </c>
-      <c r="I26" t="str">
+      <c r="I33" t="str">
         <v>recent-activity</v>
       </c>
-      <c r="J26" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27" xml:space="preserve">
-      <c r="A27" t="str">
+      <c r="J33" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34" xml:space="preserve">
+      <c r="A34" t="str">
         <v>TC-DASH-008</v>
       </c>
-      <c r="B27" t="str">
+      <c r="B34" t="str">
         <v>Dashboard</v>
       </c>
-      <c r="C27" t="str">
+      <c r="C34" t="str">
         <v>Dashboard charts render without errors</v>
       </c>
-      <c r="D27" t="str">
+      <c r="D34" t="str">
         <v>Low</v>
       </c>
-      <c r="E27" t="str">
+      <c r="E34" t="str">
         <v>User is logged in with seeded data.</v>
       </c>
-      <c r="F27" t="str" xml:space="preserve">
+      <c r="F34" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /dashboard
 2. Observe the chart panels</v>
       </c>
-      <c r="G27" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H27" t="str">
+      <c r="G34" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H34" t="str">
         <v>Monthly issues, category popularity, and returned-vs-issued charts render without console errors.</v>
       </c>
-      <c r="I27" t="str">
+      <c r="I34" t="str">
         <v>chart-monthly-issues, chart-category-popularity, chart-returned-vs-issued</v>
       </c>
-      <c r="J27" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28" xml:space="preserve">
-      <c r="A28" t="str">
+      <c r="J34" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35" xml:space="preserve">
+      <c r="A35" t="str">
+        <v>TC-DASH-009</v>
+      </c>
+      <c r="B35" t="str">
+        <v>Dashboard</v>
+      </c>
+      <c r="C35" t="str">
+        <v>Regression: Total Books minus Available Books equals Issued Books</v>
+      </c>
+      <c r="D35" t="str">
+        <v>High</v>
+      </c>
+      <c r="E35" t="str">
+        <v>A freshly seeded (or freshly reset) dataset is loaded.</v>
+      </c>
+      <c r="F35" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /dashboard
+2. Subtract Available Books from Total Books
+3. Compare the result to the Issued Books stat</v>
+      </c>
+      <c r="G35" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H35" t="str">
+        <v>The two numbers are exactly equal (e.g. 162 - 152 = 10 = Issued Books). Historically these were computed by two unrelated formulas and could disagree (e.g. 36 copies "out" vs. 12 issue records) -- this case guards against that regressing.</v>
+      </c>
+      <c r="I35" t="str">
+        <v>stat-total-books, stat-available-books, stat-issued-books</v>
+      </c>
+      <c r="J35" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36" xml:space="preserve">
+      <c r="A36" t="str">
         <v>TC-BOOK-001</v>
       </c>
-      <c r="B28" t="str">
+      <c r="B36" t="str">
         <v>Books</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C36" t="str">
         <v>Books table lists all books in the catalog</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D36" t="str">
         <v>High</v>
       </c>
-      <c r="E28" t="str">
+      <c r="E36" t="str">
         <v>User is logged in; books exist in storage.</v>
       </c>
-      <c r="F28" t="str" xml:space="preserve">
+      <c r="F36" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Observe the table</v>
       </c>
-      <c r="G28" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H28" t="str">
+      <c r="G36" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H36" t="str">
         <v>All seeded/created books appear as rows, one per book.</v>
       </c>
-      <c r="I28" t="str">
+      <c r="I36" t="str">
         <v>books-table, book-row-{id}</v>
       </c>
-      <c r="J28" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29" xml:space="preserve">
-      <c r="A29" t="str">
+      <c r="J36" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
         <v>TC-BOOK-002</v>
       </c>
-      <c r="B29" t="str">
+      <c r="B37" t="str">
         <v>Books</v>
       </c>
-      <c r="C29" t="str">
+      <c r="C37" t="str">
         <v>Search books by title returns matching results</v>
       </c>
-      <c r="D29" t="str">
+      <c r="D37" t="str">
         <v>High</v>
       </c>
-      <c r="E29" t="str">
+      <c r="E37" t="str">
         <v>A book titled "The Great Gatsby" exists.</v>
       </c>
-      <c r="F29" t="str" xml:space="preserve">
+      <c r="F37" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Type "gatsby" into the search field</v>
       </c>
-      <c r="G29" t="str">
+      <c r="G37" t="str">
         <v>search = "gatsby"</v>
       </c>
-      <c r="H29" t="str">
+      <c r="H37" t="str">
         <v>Only books whose title matches "gatsby" (case-insensitive) are shown.</v>
       </c>
-      <c r="I29" t="str">
+      <c r="I37" t="str">
         <v>books-search, books-search-field, books-table</v>
       </c>
-      <c r="J29" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30" xml:space="preserve">
-      <c r="A30" t="str">
+      <c r="J37" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38" xml:space="preserve">
+      <c r="A38" t="str">
         <v>TC-BOOK-003</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B38" t="str">
         <v>Books</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C38" t="str">
         <v>Search books by author returns matching results</v>
       </c>
-      <c r="D30" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E30" t="str">
+      <c r="D38" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E38" t="str">
         <v>A book by "J.K. Rowling" exists.</v>
       </c>
-      <c r="F30" t="str" xml:space="preserve">
+      <c r="F38" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Search by author name "rowling"</v>
       </c>
-      <c r="G30" t="str">
+      <c r="G38" t="str">
         <v>search = "rowling"</v>
       </c>
-      <c r="H30" t="str">
+      <c r="H38" t="str">
         <v>Only books authored by a matching name are shown.</v>
       </c>
-      <c r="I30" t="str">
+      <c r="I38" t="str">
         <v>books-search-field, books-table</v>
       </c>
-      <c r="J30" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
+      <c r="J38" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39" xml:space="preserve">
+      <c r="A39" t="str">
         <v>TC-BOOK-004</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B39" t="str">
         <v>Books</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C39" t="str">
         <v>Search books by ISBN returns the exact match</v>
       </c>
-      <c r="D31" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="D39" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E39" t="str">
         <v>A book with a known ISBN exists.</v>
       </c>
-      <c r="F31" t="str" xml:space="preserve">
+      <c r="F39" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Enter the full ISBN in the search field</v>
       </c>
-      <c r="G31" t="str">
+      <c r="G39" t="str">
         <v>search = "9780743273565"</v>
       </c>
-      <c r="H31" t="str">
+      <c r="H39" t="str">
         <v>Only the book with that ISBN is shown.</v>
       </c>
-      <c r="I31" t="str">
+      <c r="I39" t="str">
         <v>books-search-field, books-table</v>
       </c>
-      <c r="J31" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
-      <c r="A32" t="str">
+      <c r="J39" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40" xml:space="preserve">
+      <c r="A40" t="str">
         <v>TC-BOOK-005</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B40" t="str">
         <v>Books</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C40" t="str">
         <v>Filter books by category</v>
       </c>
-      <c r="D32" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E32" t="str">
+      <c r="D40" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E40" t="str">
         <v>Books exist across multiple categories.</v>
       </c>
-      <c r="F32" t="str" xml:space="preserve">
+      <c r="F40" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Select "Fiction" from the category filter</v>
       </c>
-      <c r="G32" t="str">
+      <c r="G40" t="str">
         <v>category = Fiction</v>
       </c>
-      <c r="H32" t="str">
+      <c r="H40" t="str">
         <v>Only books in the Fiction category are shown.</v>
       </c>
-      <c r="I32" t="str">
+      <c r="I40" t="str">
         <v>books-category-filter, books-table</v>
       </c>
-      <c r="J32" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33" xml:space="preserve">
-      <c r="A33" t="str">
+      <c r="J40" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41" xml:space="preserve">
+      <c r="A41" t="str">
         <v>TC-BOOK-006</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B41" t="str">
         <v>Books</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C41" t="str">
         <v>Filter books by availability</v>
       </c>
-      <c r="D33" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E33" t="str">
+      <c r="D41" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E41" t="str">
         <v>Both available and unavailable books exist.</v>
       </c>
-      <c r="F33" t="str" xml:space="preserve">
+      <c r="F41" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Select "Available" from the availability filter</v>
       </c>
-      <c r="G33" t="str">
+      <c r="G41" t="str">
         <v>availability = Available</v>
       </c>
-      <c r="H33" t="str">
+      <c r="H41" t="str">
         <v>Only books with availableCopies &gt; 0 are shown.</v>
       </c>
-      <c r="I33" t="str">
+      <c r="I41" t="str">
         <v>books-availability-filter, books-table</v>
       </c>
-      <c r="J33" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34" xml:space="preserve">
-      <c r="A34" t="str">
+      <c r="J41" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42" xml:space="preserve">
+      <c r="A42" t="str">
         <v>TC-BOOK-007</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B42" t="str">
         <v>Books</v>
       </c>
-      <c r="C34" t="str">
+      <c r="C42" t="str">
         <v>Clear Filters resets search and filters</v>
       </c>
-      <c r="D34" t="str">
+      <c r="D42" t="str">
         <v>Low</v>
       </c>
-      <c r="E34" t="str">
+      <c r="E42" t="str">
         <v>Search text and at least one filter are applied.</v>
       </c>
-      <c r="F34" t="str" xml:space="preserve">
+      <c r="F42" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Apply a search term and a category filter
 2. Click "Clear Filters"</v>
       </c>
-      <c r="G34" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H34" t="str">
+      <c r="G42" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H42" t="str">
         <v>Search field is cleared, filters reset to default, and the full book list is shown again.</v>
       </c>
-      <c r="I34" t="str">
+      <c r="I42" t="str">
         <v>clear-filters-button, books-search-field, books-table</v>
       </c>
-      <c r="J34" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="35" xml:space="preserve">
-      <c r="A35" t="str">
+      <c r="J42" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
         <v>TC-BOOK-008</v>
       </c>
-      <c r="B35" t="str">
+      <c r="B43" t="str">
         <v>Books</v>
       </c>
-      <c r="C35" t="str">
+      <c r="C43" t="str">
         <v>Sort books by title toggles ascending/descending</v>
       </c>
-      <c r="D35" t="str">
+      <c r="D43" t="str">
         <v>Low</v>
       </c>
-      <c r="E35" t="str">
+      <c r="E43" t="str">
         <v>Multiple books exist.</v>
       </c>
-      <c r="F35" t="str" xml:space="preserve">
+      <c r="F43" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click the Title column header
 2. Click it again</v>
       </c>
-      <c r="G35" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H35" t="str">
+      <c r="G43" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H43" t="str">
         <v>First click sorts A-Z (or reverses default), second click reverses the order.</v>
       </c>
-      <c r="I35" t="str">
+      <c r="I43" t="str">
         <v>books-table</v>
       </c>
-      <c r="J35" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36" xml:space="preserve">
-      <c r="A36" t="str">
+      <c r="J43" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str">
         <v>TC-BOOK-009</v>
       </c>
-      <c r="B36" t="str">
+      <c r="B44" t="str">
         <v>Books</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C44" t="str">
         <v>Pagination changes the number of rows shown per page</v>
       </c>
-      <c r="D36" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E36" t="str">
+      <c r="D44" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E44" t="str">
         <v>More than 10 books exist.</v>
       </c>
-      <c r="F36" t="str" xml:space="preserve">
+      <c r="F44" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /books
 2. Change page size to 25</v>
       </c>
-      <c r="G36" t="str">
+      <c r="G44" t="str">
         <v>pageSize = 25</v>
       </c>
-      <c r="H36" t="str">
+      <c r="H44" t="str">
         <v>Up to 25 rows are displayed per page; range label updates accordingly.</v>
       </c>
-      <c r="I36" t="str">
+      <c r="I44" t="str">
         <v>books-pagination-*</v>
       </c>
-      <c r="J36" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37" xml:space="preserve">
-      <c r="A37" t="str">
+      <c r="J44" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45" xml:space="preserve">
+      <c r="A45" t="str">
         <v>TC-BOOK-010</v>
       </c>
-      <c r="B37" t="str">
+      <c r="B45" t="str">
         <v>Books</v>
       </c>
-      <c r="C37" t="str">
+      <c r="C45" t="str">
         <v>Pagination Next/Prev navigates between pages</v>
       </c>
-      <c r="D37" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E37" t="str">
+      <c r="D45" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E45" t="str">
         <v>More books exist than fit on one page.</v>
       </c>
-      <c r="F37" t="str" xml:space="preserve">
+      <c r="F45" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Next
 2. Click Prev</v>
       </c>
-      <c r="G37" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H37" t="str">
+      <c r="G45" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H45" t="str">
         <v>Table content updates to show the next/previous set of rows; current page indicator updates.</v>
       </c>
-      <c r="I37" t="str">
+      <c r="I45" t="str">
         <v>books-pagination-*</v>
       </c>
-      <c r="J37" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38" xml:space="preserve">
-      <c r="A38" t="str">
+      <c r="J45" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
         <v>TC-BOOK-011</v>
       </c>
-      <c r="B38" t="str">
+      <c r="B46" t="str">
         <v>Books</v>
       </c>
-      <c r="C38" t="str">
+      <c r="C46" t="str">
         <v>Adding a new book with valid data succeeds</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D46" t="str">
         <v>High</v>
       </c>
-      <c r="E38" t="str">
+      <c r="E46" t="str">
         <v>User is on /books.</v>
       </c>
-      <c r="F38" t="str" xml:space="preserve">
+      <c r="F46" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click "Add Book"
 2. Fill in all fields with valid data
 3. Click Save</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G46" t="str">
         <v>ISBN 9780061120084, Title "To Kill a Mockingbird", Author "Harper Lee", Category Fiction, Publisher, Year 1960, Copies 4</v>
       </c>
-      <c r="H38" t="str">
+      <c r="H46" t="str">
         <v>Book is added to the table; success toast is shown; data persists in storage.</v>
       </c>
-      <c r="I38" t="str">
+      <c r="I46" t="str">
         <v>add-book-button, book-form, book-isbn, book-title, book-author, book-category, book-publisher, book-published-year, book-total-copies, save-book-button</v>
       </c>
-      <c r="J38" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str">
+      <c r="J46" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47" xml:space="preserve">
+      <c r="A47" t="str">
         <v>TC-BOOK-012</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B47" t="str">
         <v>Books</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C47" t="str">
         <v>Adding a book fails validation when required fields are missing</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D47" t="str">
         <v>High</v>
       </c>
-      <c r="E39" t="str">
+      <c r="E47" t="str">
         <v>Add Book form is open.</v>
       </c>
-      <c r="F39" t="str" xml:space="preserve">
+      <c r="F47" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Leave all fields empty
 2. Click Save</v>
       </c>
-      <c r="G39" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H39" t="str">
+      <c r="G47" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H47" t="str">
         <v>Inline error messages appear for ISBN, Title, Author, Category, Publisher, Published Year, and Number of Copies; form is not submitted.</v>
       </c>
-      <c r="I39" t="str">
+      <c r="I47" t="str">
         <v>book-form, save-book-button, *-error</v>
       </c>
-      <c r="J39" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40" xml:space="preserve">
-      <c r="A40" t="str">
+      <c r="J47" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48" xml:space="preserve">
+      <c r="A48" t="str">
         <v>TC-BOOK-013</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B48" t="str">
         <v>Books</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C48" t="str">
         <v>Adding a book fails with a duplicate ISBN</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D48" t="str">
         <v>High</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E48" t="str">
         <v>A book with ISBN 9780743273565 already exists.</v>
       </c>
-      <c r="F40" t="str" xml:space="preserve">
+      <c r="F48" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click "Add Book"
 2. Enter the existing ISBN plus other valid data
 3. Click Save</v>
       </c>
-      <c r="G40" t="str">
+      <c r="G48" t="str">
         <v>ISBN = 9780743273565 (duplicate)</v>
       </c>
-      <c r="H40" t="str">
+      <c r="H48" t="str">
         <v>Validation error indicates the ISBN already exists in the catalog; book is not added.</v>
       </c>
-      <c r="I40" t="str">
+      <c r="I48" t="str">
         <v>book-isbn, save-book-button</v>
       </c>
-      <c r="J40" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" xml:space="preserve">
-      <c r="A41" t="str">
+      <c r="J48" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49" xml:space="preserve">
+      <c r="A49" t="str">
         <v>TC-BOOK-014</v>
       </c>
-      <c r="B41" t="str">
+      <c r="B49" t="str">
         <v>Books</v>
       </c>
-      <c r="C41" t="str">
+      <c r="C49" t="str">
         <v>Adding a book fails with an invalid ISBN format</v>
       </c>
-      <c r="D41" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E41" t="str">
+      <c r="D49" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E49" t="str">
         <v>Add Book form is open.</v>
       </c>
-      <c r="F41" t="str" xml:space="preserve">
+      <c r="F49" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter "12345" as the ISBN
 2. Fill remaining fields validly
 3. Click Save</v>
       </c>
-      <c r="G41" t="str">
+      <c r="G49" t="str">
         <v>ISBN = "12345"</v>
       </c>
-      <c r="H41" t="str">
+      <c r="H49" t="str">
         <v>Validation error indicates an invalid ISBN format (must be 10 or 13 digits); book is not added.</v>
       </c>
-      <c r="I41" t="str">
+      <c r="I49" t="str">
         <v>book-isbn, save-book-button</v>
       </c>
-      <c r="J41" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42" xml:space="preserve">
-      <c r="A42" t="str">
+      <c r="J49" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50" xml:space="preserve">
+      <c r="A50" t="str">
         <v>TC-BOOK-015</v>
       </c>
-      <c r="B42" t="str">
+      <c r="B50" t="str">
         <v>Books</v>
       </c>
-      <c r="C42" t="str">
+      <c r="C50" t="str">
         <v>Editing an existing book updates its details</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D50" t="str">
         <v>High</v>
       </c>
-      <c r="E42" t="str">
+      <c r="E50" t="str">
         <v>At least one book exists.</v>
       </c>
-      <c r="F42" t="str" xml:space="preserve">
+      <c r="F50" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Edit on a book row
 2. Change the title and number of copies
 3. Click Save</v>
       </c>
-      <c r="G42" t="str">
+      <c r="G50" t="str">
         <v>New title, new copy count</v>
       </c>
-      <c r="H42" t="str">
+      <c r="H50" t="str">
         <v>Form is pre-filled with existing values; after save, the table reflects the updated data.</v>
       </c>
-      <c r="I42" t="str">
+      <c r="I50" t="str">
         <v>edit-book-{id}, book-form, save-book-button</v>
       </c>
-      <c r="J42" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43" xml:space="preserve">
-      <c r="A43" t="str">
+      <c r="J50" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51" xml:space="preserve">
+      <c r="A51" t="str">
         <v>TC-BOOK-016</v>
       </c>
-      <c r="B43" t="str">
+      <c r="B51" t="str">
         <v>Books</v>
       </c>
-      <c r="C43" t="str">
+      <c r="C51" t="str">
         <v>Deleting a book removes it after confirmation</v>
       </c>
-      <c r="D43" t="str">
+      <c r="D51" t="str">
         <v>High</v>
       </c>
-      <c r="E43" t="str">
+      <c r="E51" t="str">
         <v>At least one book exists with no active issues.</v>
       </c>
-      <c r="F43" t="str" xml:space="preserve">
+      <c r="F51" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Delete on a book row
 2. Confirm in the dialog</v>
       </c>
-      <c r="G43" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H43" t="str">
+      <c r="G51" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H51" t="str">
         <v>Confirmation dialog appears; on confirm, the book is removed from the table and storage.</v>
       </c>
-      <c r="I43" t="str">
+      <c r="I51" t="str">
         <v>delete-book-{id}, delete-book-dialog</v>
       </c>
-      <c r="J43" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
+      <c r="J51" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
         <v>TC-BOOK-017</v>
       </c>
-      <c r="B44" t="str">
+      <c r="B52" t="str">
         <v>Books</v>
       </c>
-      <c r="C44" t="str">
+      <c r="C52" t="str">
         <v>Deleting a book with active issues shows a warning</v>
       </c>
-      <c r="D44" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E44" t="str">
+      <c r="D52" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E52" t="str">
         <v>A book has at least one currently issued (unreturned) copy.</v>
       </c>
-      <c r="F44" t="str">
+      <c r="F52" t="str">
         <v>1. Click Delete on that book row</v>
       </c>
-      <c r="G44" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H44" t="str">
+      <c r="G52" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H52" t="str">
         <v>Confirmation dialog shows an additional warning about the book having active loans.</v>
       </c>
-      <c r="I44" t="str">
+      <c r="I52" t="str">
         <v>delete-book-{id}, delete-book-dialog</v>
       </c>
-      <c r="J44" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
+      <c r="J52" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>TC-BOOK-018</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B53" t="str">
         <v>Books</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C53" t="str">
         <v>Viewing a book navigates to its details page</v>
       </c>
-      <c r="D45" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E45" t="str">
+      <c r="D53" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E53" t="str">
         <v>At least one book exists.</v>
       </c>
-      <c r="F45" t="str">
+      <c r="F53" t="str">
         <v>1. Click View on a book row</v>
       </c>
-      <c r="G45" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H45" t="str">
+      <c r="G53" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H53" t="str">
         <v>App navigates to /books/{id} showing that book's full details.</v>
       </c>
-      <c r="I45" t="str">
+      <c r="I53" t="str">
         <v>view-book-{id}</v>
       </c>
-      <c r="J45" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
+      <c r="J53" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
         <v>TC-BOOK-019</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B54" t="str">
         <v>Books</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C54" t="str">
         <v>Empty state is shown when a search yields no matches</v>
       </c>
-      <c r="D46" t="str">
+      <c r="D54" t="str">
         <v>Low</v>
       </c>
-      <c r="E46" t="str">
+      <c r="E54" t="str">
         <v>User is on /books.</v>
       </c>
-      <c r="F46" t="str">
+      <c r="F54" t="str">
         <v>1. Enter a search term that matches no book, e.g. "zzzznotfound"</v>
       </c>
-      <c r="G46" t="str">
+      <c r="G54" t="str">
         <v>search = "zzzznotfound"</v>
       </c>
-      <c r="H46" t="str">
+      <c r="H54" t="str">
         <v>An empty-state message is shown instead of the table, with an option to clear filters.</v>
       </c>
-      <c r="I46" t="str">
+      <c r="I54" t="str">
         <v>books-search-field, clear-filters-button</v>
       </c>
-      <c r="J46" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
+      <c r="J54" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
         <v>TC-BOOKDET-001</v>
       </c>
-      <c r="B47" t="str">
+      <c r="B55" t="str">
         <v>Book Details</v>
       </c>
-      <c r="C47" t="str">
+      <c r="C55" t="str">
         <v>Book details page displays full book information</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D55" t="str">
         <v>High</v>
       </c>
-      <c r="E47" t="str">
+      <c r="E55" t="str">
         <v>A known book exists.</v>
       </c>
-      <c r="F47" t="str">
+      <c r="F55" t="str">
         <v>1. Navigate to /books/{id}</v>
       </c>
-      <c r="G47" t="str">
+      <c r="G55" t="str">
         <v>id of a known book</v>
       </c>
-      <c r="H47" t="str">
+      <c r="H55" t="str">
         <v>ISBN, title, author, category, publisher, year, total/available copies, description, and status are all displayed correctly.</v>
       </c>
-      <c r="I47" t="str">
+      <c r="I55" t="str">
         <v>N/A (page-level fields)</v>
       </c>
-      <c r="J47" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
+      <c r="J55" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
         <v>TC-BOOKDET-002</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B56" t="str">
         <v>Book Details</v>
       </c>
-      <c r="C48" t="str">
+      <c r="C56" t="str">
         <v>Edit button opens a pre-filled edit form</v>
       </c>
-      <c r="D48" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E48" t="str">
+      <c r="D56" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E56" t="str">
         <v>On a book's details page.</v>
       </c>
-      <c r="F48" t="str">
+      <c r="F56" t="str">
         <v>1. Click Edit</v>
       </c>
-      <c r="G48" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H48" t="str">
+      <c r="G56" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H56" t="str">
         <v>Book form modal opens with all fields pre-filled with the current book's data.</v>
       </c>
-      <c r="I48" t="str">
+      <c r="I56" t="str">
         <v>book-form</v>
       </c>
-      <c r="J48" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
+      <c r="J56" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>TC-BOOKDET-003</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B57" t="str">
         <v>Book Details</v>
       </c>
-      <c r="C49" t="str">
+      <c r="C57" t="str">
         <v>Delete button triggers a confirmation dialog</v>
       </c>
-      <c r="D49" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E49" t="str">
+      <c r="D57" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E57" t="str">
         <v>On a book's details page.</v>
       </c>
-      <c r="F49" t="str">
+      <c r="F57" t="str">
         <v>1. Click Delete</v>
       </c>
-      <c r="G49" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H49" t="str">
+      <c r="G57" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H57" t="str">
         <v>Confirmation dialog appears before any deletion occurs.</v>
       </c>
-      <c r="I49" t="str">
+      <c r="I57" t="str">
         <v>delete-book-dialog</v>
       </c>
-      <c r="J49" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50" xml:space="preserve">
-      <c r="A50" t="str">
+      <c r="J57" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
         <v>TC-BOOKDET-004</v>
       </c>
-      <c r="B50" t="str">
+      <c r="B58" t="str">
         <v>Book Details</v>
       </c>
-      <c r="C50" t="str">
+      <c r="C58" t="str">
         <v>Issue history for the book is listed, newest first</v>
       </c>
-      <c r="D50" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E50" t="str">
+      <c r="D58" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E58" t="str">
         <v>The book has at least two issue records.</v>
       </c>
-      <c r="F50" t="str" xml:space="preserve">
+      <c r="F58" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to the book's details page
 2. Observe the issue history section</v>
       </c>
-      <c r="G50" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H50" t="str">
+      <c r="G58" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H58" t="str">
         <v>All issue records referencing this book are listed, sorted by issue date descending, with member name resolved.</v>
       </c>
-      <c r="I50" t="str">
+      <c r="I58" t="str">
         <v>N/A (page-level table)</v>
       </c>
-      <c r="J50" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
+      <c r="J58" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
         <v>TC-BOOKDET-005</v>
       </c>
-      <c r="B51" t="str">
+      <c r="B59" t="str">
         <v>Book Details</v>
       </c>
-      <c r="C51" t="str">
+      <c r="C59" t="str">
         <v>Navigating to a non-existent book id shows a not-found state</v>
       </c>
-      <c r="D51" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E51" t="str">
+      <c r="D59" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E59" t="str">
         <v>No book exists with the given id.</v>
       </c>
-      <c r="F51" t="str">
+      <c r="F59" t="str">
         <v>1. Navigate to /books/DOES-NOT-EXIST</v>
       </c>
-      <c r="G51" t="str">
+      <c r="G59" t="str">
         <v>id = "DOES-NOT-EXIST"</v>
       </c>
-      <c r="H51" t="str">
+      <c r="H59" t="str">
         <v>A "book not found" message is shown with a link back to the Books list.</v>
       </c>
-      <c r="I51" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="J51" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52" xml:space="preserve">
-      <c r="A52" t="str">
+      <c r="I59" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J59" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
         <v>TC-MEM-001</v>
       </c>
-      <c r="B52" t="str">
+      <c r="B60" t="str">
         <v>Members</v>
       </c>
-      <c r="C52" t="str">
+      <c r="C60" t="str">
         <v>Members table lists all registered members</v>
       </c>
-      <c r="D52" t="str">
+      <c r="D60" t="str">
         <v>High</v>
       </c>
-      <c r="E52" t="str">
+      <c r="E60" t="str">
         <v>Members exist in storage.</v>
       </c>
-      <c r="F52" t="str" xml:space="preserve">
+      <c r="F60" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /members
 2. Observe the table</v>
       </c>
-      <c r="G52" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H52" t="str">
+      <c r="G60" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H60" t="str">
         <v>All members appear as rows, one per member.</v>
       </c>
-      <c r="I52" t="str">
+      <c r="I60" t="str">
         <v>members-table, member-row-{id}</v>
       </c>
-      <c r="J52" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53" xml:space="preserve">
-      <c r="A53" t="str">
+      <c r="J60" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61" xml:space="preserve">
+      <c r="A61" t="str">
         <v>TC-MEM-002</v>
       </c>
-      <c r="B53" t="str">
+      <c r="B61" t="str">
         <v>Members</v>
       </c>
-      <c r="C53" t="str">
+      <c r="C61" t="str">
         <v>Search members by name returns matching results</v>
       </c>
-      <c r="D53" t="str">
+      <c r="D61" t="str">
         <v>High</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E61" t="str">
         <v>A member named "Aarav Sharma" exists.</v>
       </c>
-      <c r="F53" t="str" xml:space="preserve">
+      <c r="F61" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /members
 2. Search "aarav"</v>
       </c>
-      <c r="G53" t="str">
+      <c r="G61" t="str">
         <v>search = "aarav"</v>
       </c>
-      <c r="H53" t="str">
+      <c r="H61" t="str">
         <v>Only members matching the name (case-insensitive) are shown.</v>
       </c>
-      <c r="I53" t="str">
+      <c r="I61" t="str">
         <v>member-search, members-table</v>
       </c>
-      <c r="J53" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str">
+      <c r="J61" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62" xml:space="preserve">
+      <c r="A62" t="str">
         <v>TC-MEM-003</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B62" t="str">
         <v>Members</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C62" t="str">
         <v>Search members by email returns matching results</v>
       </c>
-      <c r="D54" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E54" t="str">
+      <c r="D62" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E62" t="str">
         <v>A member with a known email exists.</v>
       </c>
-      <c r="F54" t="str" xml:space="preserve">
+      <c r="F62" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /members
 2. Search by that email</v>
       </c>
-      <c r="G54" t="str">
+      <c r="G62" t="str">
         <v>search = "aarav.sharma@mail.com"</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H62" t="str">
         <v>Only the matching member is shown.</v>
       </c>
-      <c r="I54" t="str">
+      <c r="I62" t="str">
         <v>member-search, members-table</v>
       </c>
-      <c r="J54" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
+      <c r="J62" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
         <v>TC-MEM-004</v>
       </c>
-      <c r="B55" t="str">
+      <c r="B63" t="str">
         <v>Members</v>
       </c>
-      <c r="C55" t="str">
+      <c r="C63" t="str">
         <v>Filter members by membership type</v>
       </c>
-      <c r="D55" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E55" t="str">
+      <c r="D63" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E63" t="str">
         <v>Members of different types (Basic/Premium/Student) exist.</v>
       </c>
-      <c r="F55" t="str">
+      <c r="F63" t="str">
         <v>1. Select "Premium" in the membership type filter</v>
       </c>
-      <c r="G55" t="str">
+      <c r="G63" t="str">
         <v>type = Premium</v>
       </c>
-      <c r="H55" t="str">
+      <c r="H63" t="str">
         <v>Only Premium members are shown.</v>
       </c>
-      <c r="I55" t="str">
+      <c r="I63" t="str">
         <v>member-type-filter, members-table</v>
       </c>
-      <c r="J55" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
+      <c r="J63" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
         <v>TC-MEM-005</v>
       </c>
-      <c r="B56" t="str">
+      <c r="B64" t="str">
         <v>Members</v>
       </c>
-      <c r="C56" t="str">
+      <c r="C64" t="str">
         <v>Filter members by status</v>
       </c>
-      <c r="D56" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E56" t="str">
+      <c r="D64" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E64" t="str">
         <v>Both Active and Inactive members exist.</v>
       </c>
-      <c r="F56" t="str">
+      <c r="F64" t="str">
         <v>1. Select "Inactive" in the status filter</v>
       </c>
-      <c r="G56" t="str">
+      <c r="G64" t="str">
         <v>status = Inactive</v>
       </c>
-      <c r="H56" t="str">
+      <c r="H64" t="str">
         <v>Only Inactive members are shown.</v>
       </c>
-      <c r="I56" t="str">
+      <c r="I64" t="str">
         <v>member-status-filter, members-table</v>
       </c>
-      <c r="J56" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
+      <c r="J64" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
         <v>TC-MEM-006</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B65" t="str">
         <v>Members</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C65" t="str">
         <v>Pagination works on the members list</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D65" t="str">
         <v>Low</v>
       </c>
-      <c r="E57" t="str">
+      <c r="E65" t="str">
         <v>More than 10 members exist.</v>
       </c>
-      <c r="F57" t="str">
+      <c r="F65" t="str">
         <v>1. Change page size and navigate pages</v>
       </c>
-      <c r="G57" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H57" t="str">
+      <c r="G65" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H65" t="str">
         <v>Rows per page and page navigation behave correctly, matching the Books page pattern.</v>
       </c>
-      <c r="I57" t="str">
+      <c r="I65" t="str">
         <v>members-table</v>
       </c>
-      <c r="J57" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
+      <c r="J65" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66" xml:space="preserve">
+      <c r="A66" t="str">
         <v>TC-MEM-007</v>
       </c>
-      <c r="B58" t="str">
+      <c r="B66" t="str">
         <v>Members</v>
       </c>
-      <c r="C58" t="str">
+      <c r="C66" t="str">
         <v>Registering a new member with valid data succeeds</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D66" t="str">
         <v>High</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E66" t="str">
         <v>User is on /members.</v>
       </c>
-      <c r="F58" t="str" xml:space="preserve">
+      <c r="F66" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click "Add Member"
 2. Fill in all fields with valid data
 3. Click Register</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G66" t="str">
         <v>First "Isha", Last "Verma", email isha.verma@mail.com, phone 9812345678, DOB 1995-05-20, address, membership type Basic, expiry date</v>
       </c>
-      <c r="H58" t="str">
+      <c r="H66" t="str">
         <v>Member is added to the table; success toast shown; data persists in storage.</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I66" t="str">
         <v>add-member-button, member-form, member-first-name, member-last-name, member-email, member-phone, member-dob, member-address, member-membership-type, member-membership-expiry, save-member-button</v>
       </c>
-      <c r="J58" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59" xml:space="preserve">
-      <c r="A59" t="str">
+      <c r="J66" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67" xml:space="preserve">
+      <c r="A67" t="str">
         <v>TC-MEM-008</v>
       </c>
-      <c r="B59" t="str">
+      <c r="B67" t="str">
         <v>Members</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C67" t="str">
         <v>Registering a member fails with an invalid email</v>
       </c>
-      <c r="D59" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E59" t="str">
+      <c r="D67" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E67" t="str">
         <v>Add Member form is open.</v>
       </c>
-      <c r="F59" t="str" xml:space="preserve">
+      <c r="F67" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter "not-an-email" in the email field
 2. Fill remaining fields validly
 3. Click Register</v>
       </c>
-      <c r="G59" t="str">
+      <c r="G67" t="str">
         <v>email = "not-an-email"</v>
       </c>
-      <c r="H59" t="str">
+      <c r="H67" t="str">
         <v>Validation error indicates an invalid email; member is not created.</v>
       </c>
-      <c r="I59" t="str">
+      <c r="I67" t="str">
         <v>member-email, save-member-button</v>
       </c>
-      <c r="J59" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60" t="str">
+      <c r="J67" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68" xml:space="preserve">
+      <c r="A68" t="str">
         <v>TC-MEM-009</v>
       </c>
-      <c r="B60" t="str">
+      <c r="B68" t="str">
         <v>Members</v>
       </c>
-      <c r="C60" t="str">
+      <c r="C68" t="str">
         <v>Registering a member fails with an invalid phone number</v>
       </c>
-      <c r="D60" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E60" t="str">
+      <c r="D68" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E68" t="str">
         <v>Add Member form is open.</v>
       </c>
-      <c r="F60" t="str" xml:space="preserve">
+      <c r="F68" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter "123" in the phone field
 2. Fill remaining fields validly
 3. Click Register</v>
       </c>
-      <c r="G60" t="str">
+      <c r="G68" t="str">
         <v>phone = "123"</v>
       </c>
-      <c r="H60" t="str">
+      <c r="H68" t="str">
         <v>Validation error indicates an invalid phone number (10-13 digits required); member is not created.</v>
       </c>
-      <c r="I60" t="str">
+      <c r="I68" t="str">
         <v>member-phone, save-member-button</v>
       </c>
-      <c r="J60" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61" xml:space="preserve">
-      <c r="A61" t="str">
+      <c r="J68" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69" xml:space="preserve">
+      <c r="A69" t="str">
         <v>TC-MEM-010</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B69" t="str">
         <v>Members</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C69" t="str">
         <v>Registering a member fails with a duplicate email</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D69" t="str">
         <v>High</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E69" t="str">
         <v>A member with email "isha.verma@mail.com" already exists.</v>
       </c>
-      <c r="F61" t="str" xml:space="preserve">
+      <c r="F69" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter that email for a new member
 2. Fill remaining fields validly
 3. Click Register</v>
       </c>
-      <c r="G61" t="str">
+      <c r="G69" t="str">
         <v>email = "isha.verma@mail.com" (duplicate)</v>
       </c>
-      <c r="H61" t="str">
+      <c r="H69" t="str">
         <v>Validation error indicates a member with this email already exists; member is not created.</v>
       </c>
-      <c r="I61" t="str">
+      <c r="I69" t="str">
         <v>member-email, save-member-button</v>
       </c>
-      <c r="J61" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62" xml:space="preserve">
-      <c r="A62" t="str">
+      <c r="J69" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70" xml:space="preserve">
+      <c r="A70" t="str">
         <v>TC-MEM-011</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B70" t="str">
         <v>Members</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C70" t="str">
         <v>Editing an existing member updates their details</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D70" t="str">
         <v>High</v>
       </c>
-      <c r="E62" t="str">
+      <c r="E70" t="str">
         <v>At least one member exists.</v>
       </c>
-      <c r="F62" t="str" xml:space="preserve">
+      <c r="F70" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Edit on a member row
 2. Change phone and address
 3. Click Save</v>
       </c>
-      <c r="G62" t="str">
+      <c r="G70" t="str">
         <v>New phone, new address</v>
       </c>
-      <c r="H62" t="str">
+      <c r="H70" t="str">
         <v>Form pre-fills existing data; after save, the table reflects the updated member details.</v>
       </c>
-      <c r="I62" t="str">
+      <c r="I70" t="str">
         <v>edit-member-{id}, member-form, save-member-button</v>
       </c>
-      <c r="J62" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63" xml:space="preserve">
-      <c r="A63" t="str">
+      <c r="J70" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71" xml:space="preserve">
+      <c r="A71" t="str">
         <v>TC-MEM-012</v>
       </c>
-      <c r="B63" t="str">
+      <c r="B71" t="str">
         <v>Members</v>
       </c>
-      <c r="C63" t="str">
+      <c r="C71" t="str">
         <v>Deleting a member removes them after confirmation</v>
       </c>
-      <c r="D63" t="str">
+      <c r="D71" t="str">
         <v>High</v>
       </c>
-      <c r="E63" t="str">
+      <c r="E71" t="str">
         <v>A member with no active loans exists.</v>
       </c>
-      <c r="F63" t="str" xml:space="preserve">
+      <c r="F71" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Delete on the member row
 2. Confirm in the dialog</v>
       </c>
-      <c r="G63" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H63" t="str">
+      <c r="G71" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H71" t="str">
         <v>Confirmation dialog appears; on confirm, the member is removed from the table and storage.</v>
       </c>
-      <c r="I63" t="str">
+      <c r="I71" t="str">
         <v>delete-member-{id}, delete-member-dialog</v>
       </c>
-      <c r="J63" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
+      <c r="J71" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
         <v>TC-MEM-013</v>
       </c>
-      <c r="B64" t="str">
+      <c r="B72" t="str">
         <v>Members</v>
       </c>
-      <c r="C64" t="str">
+      <c r="C72" t="str">
         <v>Deleting a member with active loans shows a warning</v>
       </c>
-      <c r="D64" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E64" t="str">
+      <c r="D72" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E72" t="str">
         <v>A member currently has one or more books issued.</v>
       </c>
-      <c r="F64" t="str">
+      <c r="F72" t="str">
         <v>1. Click Delete on that member's row</v>
       </c>
-      <c r="G64" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H64" t="str">
+      <c r="G72" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H72" t="str">
         <v>Confirmation dialog shows an additional warning about the member's active loans.</v>
       </c>
-      <c r="I64" t="str">
+      <c r="I72" t="str">
         <v>delete-member-{id}, delete-member-dialog</v>
       </c>
-      <c r="J64" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
+      <c r="J72" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
         <v>TC-MEM-014</v>
       </c>
-      <c r="B65" t="str">
+      <c r="B73" t="str">
         <v>Members</v>
       </c>
-      <c r="C65" t="str">
+      <c r="C73" t="str">
         <v>Viewing a member navigates to their details page</v>
       </c>
-      <c r="D65" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E65" t="str">
+      <c r="D73" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E73" t="str">
         <v>At least one member exists.</v>
       </c>
-      <c r="F65" t="str">
+      <c r="F73" t="str">
         <v>1. Click View on a member row</v>
       </c>
-      <c r="G65" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H65" t="str">
+      <c r="G73" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H73" t="str">
         <v>App navigates to /members/{id} showing that member's full profile.</v>
       </c>
-      <c r="I65" t="str">
+      <c r="I73" t="str">
         <v>view-member-{id}</v>
       </c>
-      <c r="J65" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
+      <c r="J73" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
         <v>TC-MEMDET-001</v>
       </c>
-      <c r="B66" t="str">
+      <c r="B74" t="str">
         <v>Member Details</v>
       </c>
-      <c r="C66" t="str">
+      <c r="C74" t="str">
         <v>Member details page displays full profile information</v>
       </c>
-      <c r="D66" t="str">
+      <c r="D74" t="str">
         <v>High</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E74" t="str">
         <v>A known member exists.</v>
       </c>
-      <c r="F66" t="str">
+      <c r="F74" t="str">
         <v>1. Navigate to /members/{id}</v>
       </c>
-      <c r="G66" t="str">
+      <c r="G74" t="str">
         <v>id of a known member</v>
       </c>
-      <c r="H66" t="str">
+      <c r="H74" t="str">
         <v>Name, email, phone, DOB, address, membership type/dates, status, and join date are all displayed correctly.</v>
       </c>
-      <c r="I66" t="str">
+      <c r="I74" t="str">
         <v>N/A (page-level fields)</v>
       </c>
-      <c r="J66" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
+      <c r="J74" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>TC-MEMDET-002</v>
       </c>
-      <c r="B67" t="str">
+      <c r="B75" t="str">
         <v>Member Details</v>
       </c>
-      <c r="C67" t="str">
+      <c r="C75" t="str">
         <v>Edit button opens a pre-filled edit form</v>
       </c>
-      <c r="D67" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E67" t="str">
+      <c r="D75" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E75" t="str">
         <v>On a member's details page.</v>
       </c>
-      <c r="F67" t="str">
+      <c r="F75" t="str">
         <v>1. Click Edit</v>
       </c>
-      <c r="G67" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H67" t="str">
+      <c r="G75" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H75" t="str">
         <v>Member form modal opens pre-filled with the current member's data.</v>
       </c>
-      <c r="I67" t="str">
+      <c r="I75" t="str">
         <v>member-form</v>
       </c>
-      <c r="J67" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K67" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
+      <c r="J75" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
         <v>TC-MEMDET-003</v>
       </c>
-      <c r="B68" t="str">
+      <c r="B76" t="str">
         <v>Member Details</v>
       </c>
-      <c r="C68" t="str">
+      <c r="C76" t="str">
         <v>Delete button triggers a confirmation dialog</v>
       </c>
-      <c r="D68" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E68" t="str">
+      <c r="D76" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E76" t="str">
         <v>On a member's details page.</v>
       </c>
-      <c r="F68" t="str">
+      <c r="F76" t="str">
         <v>1. Click Delete</v>
       </c>
-      <c r="G68" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H68" t="str">
+      <c r="G76" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H76" t="str">
         <v>Confirmation dialog appears before any deletion occurs.</v>
       </c>
-      <c r="I68" t="str">
+      <c r="I76" t="str">
         <v>delete-member-dialog</v>
       </c>
-      <c r="J68" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69" xml:space="preserve">
-      <c r="A69" t="str">
+      <c r="J76" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77" xml:space="preserve">
+      <c r="A77" t="str">
         <v>TC-MEMDET-004</v>
       </c>
-      <c r="B69" t="str">
+      <c r="B77" t="str">
         <v>Member Details</v>
       </c>
-      <c r="C69" t="str">
+      <c r="C77" t="str">
         <v>Borrowing history displays issues with correct fines</v>
       </c>
-      <c r="D69" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E69" t="str">
+      <c r="D77" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E77" t="str">
         <v>The member has at least one returned overdue issue and one active issue.</v>
       </c>
-      <c r="F69" t="str" xml:space="preserve">
+      <c r="F77" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to the member's details page
 2. Observe the issue history section</v>
       </c>
-      <c r="G69" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H69" t="str">
+      <c r="G77" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H77" t="str">
         <v>All issues for this member are listed with correct book title, status, and fine amount (₹10/day overdue).</v>
       </c>
-      <c r="I69" t="str">
+      <c r="I77" t="str">
         <v>N/A (page-level table)</v>
       </c>
-      <c r="J69" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
+      <c r="J77" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
         <v>TC-MEMDET-005</v>
       </c>
-      <c r="B70" t="str">
+      <c r="B78" t="str">
         <v>Member Details</v>
       </c>
-      <c r="C70" t="str">
+      <c r="C78" t="str">
         <v>Navigating to a non-existent member id shows a not-found state</v>
       </c>
-      <c r="D70" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E70" t="str">
+      <c r="D78" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E78" t="str">
         <v>No member exists with the given id.</v>
       </c>
-      <c r="F70" t="str">
+      <c r="F78" t="str">
         <v>1. Navigate to /members/DOES-NOT-EXIST</v>
       </c>
-      <c r="G70" t="str">
+      <c r="G78" t="str">
         <v>id = "DOES-NOT-EXIST"</v>
       </c>
-      <c r="H70" t="str">
+      <c r="H78" t="str">
         <v>A "member not found" message is shown with a link back to the Members list.</v>
       </c>
-      <c r="I70" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="J70" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71" xml:space="preserve">
-      <c r="A71" t="str">
+      <c r="I78" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79" xml:space="preserve">
+      <c r="A79" t="str">
         <v>TC-ISSUE-001</v>
       </c>
-      <c r="B71" t="str">
+      <c r="B79" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C71" t="str">
+      <c r="C79" t="str">
         <v>Issue an available book to an eligible member</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D79" t="str">
         <v>High</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E79" t="str">
         <v>A book with availableCopies &gt; 0 and a member with fewer than 5 active loans both exist.</v>
       </c>
-      <c r="F71" t="str" xml:space="preserve">
+      <c r="F79" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /issue-book
 2. Select the member
 3. Select the book
 4. Set issue/due dates
 5. Click Issue</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G79" t="str">
         <v>Valid member + valid available book</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H79" t="str">
         <v>Issue record is created with status "Issued"; success toast is shown.</v>
       </c>
-      <c r="I71" t="str">
+      <c r="I79" t="str">
         <v>issue-select-member, issue-select-book, issue-date, issue-due-date, issue-book-button</v>
       </c>
-      <c r="J71" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72" xml:space="preserve">
-      <c r="A72" t="str">
+      <c r="J79" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80" xml:space="preserve">
+      <c r="A80" t="str">
         <v>TC-ISSUE-002</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B80" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C72" t="str">
+      <c r="C80" t="str">
         <v>Issuing a book decrements its available copies</v>
       </c>
-      <c r="D72" t="str">
+      <c r="D80" t="str">
         <v>High</v>
       </c>
-      <c r="E72" t="str">
+      <c r="E80" t="str">
         <v>A book has availableCopies = N (N &gt; 0).</v>
       </c>
-      <c r="F72" t="str" xml:space="preserve">
+      <c r="F80" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Issue that book to a member
 2. Navigate to /books and check the book's available copies</v>
       </c>
-      <c r="G72" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H72" t="str">
+      <c r="G80" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H80" t="str">
         <v>availableCopies is reduced by 1 (N-1); status becomes "Unavailable" if it reaches 0.</v>
       </c>
-      <c r="I72" t="str">
+      <c r="I80" t="str">
         <v>issue-book-button</v>
       </c>
-      <c r="J72" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73" t="str">
+      <c r="J80" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81" xml:space="preserve">
+      <c r="A81" t="str">
         <v>TC-ISSUE-003</v>
       </c>
-      <c r="B73" t="str">
+      <c r="B81" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C73" t="str">
+      <c r="C81" t="str">
         <v>Cannot issue a book with zero available copies</v>
       </c>
-      <c r="D73" t="str">
+      <c r="D81" t="str">
         <v>High</v>
       </c>
-      <c r="E73" t="str">
+      <c r="E81" t="str">
         <v>A book has availableCopies = 0.</v>
       </c>
-      <c r="F73" t="str" xml:space="preserve">
+      <c r="F81" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /issue-book
 2. Attempt to select/issue that book</v>
       </c>
-      <c r="G73" t="str">
+      <c r="G81" t="str">
         <v>Book with 0 available copies</v>
       </c>
-      <c r="H73" t="str">
+      <c r="H81" t="str">
         <v>The book is not selectable, or an explicit validation error blocks the issue attempt.</v>
       </c>
-      <c r="I73" t="str">
+      <c r="I81" t="str">
         <v>issue-select-book, issue-book-button</v>
       </c>
-      <c r="J73" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K73" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="74" xml:space="preserve">
-      <c r="A74" t="str">
+      <c r="J81" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82" xml:space="preserve">
+      <c r="A82" t="str">
         <v>TC-ISSUE-004</v>
       </c>
-      <c r="B74" t="str">
+      <c r="B82" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C74" t="str">
-        <v>Cannot issue a book to a member who already has 5 active loans</v>
-      </c>
-      <c r="D74" t="str">
+      <c r="C82" t="str">
+        <v>Cannot issue a book to a Basic member who already has 5 active loans</v>
+      </c>
+      <c r="D82" t="str">
         <v>High</v>
       </c>
-      <c r="E74" t="str">
-        <v>A member already has 5 currently-issued (unreturned) books.</v>
-      </c>
-      <c r="F74" t="str" xml:space="preserve">
+      <c r="E82" t="str">
+        <v>A Basic-membership member already has 5 currently-issued (unreturned) books.</v>
+      </c>
+      <c r="F82" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /issue-book
 2. Select that member
 3. Attempt to issue any available book</v>
       </c>
-      <c r="G74" t="str">
-        <v>Member with 5 active issues</v>
-      </c>
-      <c r="H74" t="str">
-        <v>Validation error blocks the issue, referencing the 5-book limit.</v>
-      </c>
-      <c r="I74" t="str">
-        <v>issue-select-member, issue-book-button</v>
-      </c>
-      <c r="J74" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75" xml:space="preserve">
-      <c r="A75" t="str">
+      <c r="G82" t="str">
+        <v>Basic member with 5 active issues</v>
+      </c>
+      <c r="H82" t="str">
+        <v>Validation error blocks the issue: "This member already has 5 books issued (the maximum allowed)."</v>
+      </c>
+      <c r="I82" t="str">
+        <v>issue-select-member, issue-book-button, member-issue-summary</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
         <v>TC-ISSUE-005</v>
       </c>
-      <c r="B75" t="str">
+      <c r="B83" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C75" t="str">
+      <c r="C83" t="str">
+        <v>Cannot issue a book to a Student member who already has 3 active loans</v>
+      </c>
+      <c r="D83" t="str">
+        <v>High</v>
+      </c>
+      <c r="E83" t="str">
+        <v>A Student-membership member already has 3 currently-issued (unreturned) books.</v>
+      </c>
+      <c r="F83" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /issue-book
+2. Select that member
+3. Attempt to issue any available book</v>
+      </c>
+      <c r="G83" t="str">
+        <v>Student member with 3 active issues</v>
+      </c>
+      <c r="H83" t="str">
+        <v>Validation error blocks the issue: "This member already has 3 books issued (the maximum allowed)."</v>
+      </c>
+      <c r="I83" t="str">
+        <v>issue-select-member, issue-book-button, member-issue-summary</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84" xml:space="preserve">
+      <c r="A84" t="str">
+        <v>TC-ISSUE-006</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Issue Book</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Premium members have no active-loan cap</v>
+      </c>
+      <c r="D84" t="str">
+        <v>High</v>
+      </c>
+      <c r="E84" t="str">
+        <v>A Premium-membership member already has 5+ currently-issued (unreturned) books.</v>
+      </c>
+      <c r="F84" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /issue-book
+2. Select that Premium member
+3. Select any available book
+4. Click Issue</v>
+      </c>
+      <c r="G84" t="str">
+        <v>Premium member with 5+ active issues</v>
+      </c>
+      <c r="H84" t="str">
+        <v>No member-limit validation error appears; the confirm-issue dialog opens normally and the issue can be completed.</v>
+      </c>
+      <c r="I84" t="str">
+        <v>issue-select-member, member-issue-summary, confirm-issue-dialog</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85" xml:space="preserve">
+      <c r="A85" t="str">
+        <v>TC-ISSUE-007</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Issue Book</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Member issue summary shows the correct limit per membership type</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Members of each type (Basic/Student/Premium) exist.</v>
+      </c>
+      <c r="F85" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Select a Basic member, observe the summary
+2. Select a Student member, observe the summary
+3. Select a Premium member, observe the summary</v>
+      </c>
+      <c r="G85" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H85" t="str">
+        <v>Summary reads "Currently issued: X / 5" for Basic, "X / 3" for Student, and "X / ∞" (infinity) for Premium.</v>
+      </c>
+      <c r="I85" t="str">
+        <v>member-issue-summary</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
+        <v>TC-ISSUE-008</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Issue Book</v>
+      </c>
+      <c r="C86" t="str">
         <v>Due date must be on or after the issue date</v>
       </c>
-      <c r="D75" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E75" t="str">
+      <c r="D86" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E86" t="str">
         <v>On the Issue Book page.</v>
       </c>
-      <c r="F75" t="str" xml:space="preserve">
+      <c r="F86" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Set a due date earlier than the issue date
 2. Click Issue</v>
       </c>
-      <c r="G75" t="str">
+      <c r="G86" t="str">
         <v>issueDate = today, dueDate = yesterday</v>
       </c>
-      <c r="H75" t="str">
+      <c r="H86" t="str">
         <v>Validation error indicates the due date cannot be earlier than the issue date; issue is blocked.</v>
       </c>
-      <c r="I75" t="str">
+      <c r="I86" t="str">
         <v>issue-date, issue-due-date, issue-book-button</v>
       </c>
-      <c r="J75" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76" t="str">
-        <v>TC-ISSUE-006</v>
-      </c>
-      <c r="B76" t="str">
+      <c r="J86" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87" xml:space="preserve">
+      <c r="A87" t="str">
+        <v>TC-ISSUE-009</v>
+      </c>
+      <c r="B87" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C76" t="str">
+      <c r="C87" t="str">
         <v>Issue date cannot be set in the past</v>
       </c>
-      <c r="D76" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E76" t="str">
+      <c r="D87" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E87" t="str">
         <v>On the Issue Book page.</v>
       </c>
-      <c r="F76" t="str" xml:space="preserve">
+      <c r="F87" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Set the issue date to a past date
 2. Click Issue</v>
       </c>
-      <c r="G76" t="str">
+      <c r="G87" t="str">
         <v>issueDate = yesterday</v>
       </c>
-      <c r="H76" t="str">
+      <c r="H87" t="str">
         <v>Validation error indicates the issue date cannot be in the past; issue is blocked.</v>
       </c>
-      <c r="I76" t="str">
+      <c r="I87" t="str">
         <v>issue-date, issue-book-button</v>
       </c>
-      <c r="J76" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K76" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>TC-ISSUE-007</v>
-      </c>
-      <c r="B77" t="str">
+      <c r="J87" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>TC-ISSUE-010</v>
+      </c>
+      <c r="B88" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C77" t="str">
+      <c r="C88" t="str">
         <v>Confirmation dialog appears before finalizing an issue</v>
       </c>
-      <c r="D77" t="str">
+      <c r="D88" t="str">
         <v>Low</v>
       </c>
-      <c r="E77" t="str">
+      <c r="E88" t="str">
         <v>Valid member and book selected on the Issue Book page.</v>
       </c>
-      <c r="F77" t="str">
+      <c r="F88" t="str">
         <v>1. Click Issue</v>
       </c>
-      <c r="G77" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H77" t="str">
+      <c r="G88" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H88" t="str">
         <v>Confirmation dialog summarizes the issue details before it is committed.</v>
       </c>
-      <c r="I77" t="str">
+      <c r="I88" t="str">
         <v>confirm-issue-dialog</v>
       </c>
-      <c r="J77" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>TC-ISSUE-008</v>
-      </c>
-      <c r="B78" t="str">
+      <c r="J88" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>TC-ISSUE-011</v>
+      </c>
+      <c r="B89" t="str">
         <v>Issue Book</v>
       </c>
-      <c r="C78" t="str">
+      <c r="C89" t="str">
         <v>Success message is shown after a book is issued</v>
       </c>
-      <c r="D78" t="str">
+      <c r="D89" t="str">
         <v>Low</v>
       </c>
-      <c r="E78" t="str">
+      <c r="E89" t="str">
         <v>Issue completes successfully.</v>
       </c>
-      <c r="F78" t="str">
+      <c r="F89" t="str">
         <v>1. Complete a valid issue flow</v>
       </c>
-      <c r="G78" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H78" t="str">
+      <c r="G89" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H89" t="str">
         <v>A success toast confirms the book was issued.</v>
       </c>
-      <c r="I78" t="str">
+      <c r="I89" t="str">
         <v>toast-success</v>
       </c>
-      <c r="J78" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79" xml:space="preserve">
-      <c r="A79" t="str">
+      <c r="J89" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90" xml:space="preserve">
+      <c r="A90" t="str">
         <v>TC-RETURN-001</v>
       </c>
-      <c r="B79" t="str">
+      <c r="B90" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C79" t="str">
+      <c r="C90" t="str">
         <v>Returning a book on time applies no fine</v>
       </c>
-      <c r="D79" t="str">
+      <c r="D90" t="str">
         <v>High</v>
       </c>
-      <c r="E79" t="str">
+      <c r="E90" t="str">
         <v>An issue exists with status Issued and a due date in the future (or today).</v>
       </c>
-      <c r="F79" t="str" xml:space="preserve">
+      <c r="F90" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /return-books
 2. Locate the issue
 3. Click Return
 4. Confirm</v>
       </c>
-      <c r="G79" t="str">
+      <c r="G90" t="str">
         <v>dueDate &gt;= today</v>
       </c>
-      <c r="H79" t="str">
+      <c r="H90" t="str">
         <v>Issue status becomes "Returned"; fine = ₹0.</v>
       </c>
-      <c r="I79" t="str">
+      <c r="I90" t="str">
         <v>return-books-table, return-book-button-{id}, confirm-return-dialog</v>
       </c>
-      <c r="J79" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K79" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="80" xml:space="preserve">
-      <c r="A80" t="str">
+      <c r="J90" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91" xml:space="preserve">
+      <c r="A91" t="str">
         <v>TC-RETURN-002</v>
       </c>
-      <c r="B80" t="str">
+      <c r="B91" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C80" t="str">
+      <c r="C91" t="str">
         <v>Returning an overdue book calculates the correct fine</v>
       </c>
-      <c r="D80" t="str">
+      <c r="D91" t="str">
         <v>High</v>
       </c>
-      <c r="E80" t="str">
+      <c r="E91" t="str">
         <v>An issue exists with status Overdue, due date N days in the past.</v>
       </c>
-      <c r="F80" t="str" xml:space="preserve">
+      <c r="F91" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /return-books
 2. Return the overdue issue</v>
       </c>
-      <c r="G80" t="str">
+      <c r="G91" t="str">
         <v>N days overdue (e.g. 5)</v>
       </c>
-      <c r="H80" t="str">
+      <c r="H91" t="str">
         <v>Fine = N x ₹10 (e.g. 5 days -&gt; ₹50); issue status becomes "Returned" with that fine recorded.</v>
       </c>
-      <c r="I80" t="str">
+      <c r="I91" t="str">
         <v>return-book-button-{id}, confirm-return-dialog</v>
       </c>
-      <c r="J80" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81" xml:space="preserve">
-      <c r="A81" t="str">
+      <c r="J91" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str">
         <v>TC-RETURN-003</v>
       </c>
-      <c r="B81" t="str">
+      <c r="B92" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C81" t="str">
+      <c r="C92" t="str">
         <v>Returning a book increments the book's available copies</v>
       </c>
-      <c r="D81" t="str">
+      <c r="D92" t="str">
         <v>High</v>
       </c>
-      <c r="E81" t="str">
+      <c r="E92" t="str">
         <v>A book currently has one copy out on loan.</v>
       </c>
-      <c r="F81" t="str" xml:space="preserve">
+      <c r="F92" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Return that issue
 2. Check the book's available copies on /books</v>
       </c>
-      <c r="G81" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H81" t="str">
+      <c r="G92" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H92" t="str">
         <v>availableCopies increases by 1; status becomes "Available" again if previously 0.</v>
       </c>
-      <c r="I81" t="str">
+      <c r="I92" t="str">
         <v>return-book-button-{id}</v>
       </c>
-      <c r="J81" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82" xml:space="preserve">
-      <c r="A82" t="str">
+      <c r="J92" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93" xml:space="preserve">
+      <c r="A93" t="str">
         <v>TC-RETURN-004</v>
       </c>
-      <c r="B82" t="str">
+      <c r="B93" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C82" t="str">
+      <c r="C93" t="str">
         <v>Returning a book decrements the member's active loan count</v>
       </c>
-      <c r="D82" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E82" t="str">
+      <c r="D93" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E93" t="str">
         <v>A member has 1+ active issues.</v>
       </c>
-      <c r="F82" t="str" xml:space="preserve">
+      <c r="F93" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Return one of that member's issues
 2. Check the member's details page</v>
       </c>
-      <c r="G82" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H82" t="str">
+      <c r="G93" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H93" t="str">
         <v>Member's active/issued book count is reduced by 1.</v>
       </c>
-      <c r="I82" t="str">
+      <c r="I93" t="str">
         <v>return-book-button-{id}</v>
       </c>
-      <c r="J82" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
+      <c r="J93" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
         <v>TC-RETURN-005</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B94" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C83" t="str">
+      <c r="C94" t="str">
         <v>Confirmation dialog appears before finalizing a return</v>
       </c>
-      <c r="D83" t="str">
+      <c r="D94" t="str">
         <v>Low</v>
       </c>
-      <c r="E83" t="str">
+      <c r="E94" t="str">
         <v>On the Return Books page with an active issue.</v>
       </c>
-      <c r="F83" t="str">
+      <c r="F94" t="str">
         <v>1. Click Return on a row</v>
       </c>
-      <c r="G83" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H83" t="str">
+      <c r="G94" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H94" t="str">
         <v>Confirmation dialog shows details of the return (and fine, if any) before committing.</v>
       </c>
-      <c r="I83" t="str">
+      <c r="I94" t="str">
         <v>confirm-return-dialog</v>
       </c>
-      <c r="J83" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K83" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="84" xml:space="preserve">
-      <c r="A84" t="str">
+      <c r="J94" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95" xml:space="preserve">
+      <c r="A95" t="str">
         <v>TC-RETURN-006</v>
       </c>
-      <c r="B84" t="str">
+      <c r="B95" t="str">
         <v>Return Books</v>
       </c>
-      <c r="C84" t="str">
+      <c r="C95" t="str">
         <v>Return Books page lists only currently active (unreturned) issues</v>
       </c>
-      <c r="D84" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E84" t="str">
+      <c r="D95" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E95" t="str">
         <v>A mix of Issued, Overdue, and Returned issue records exist.</v>
       </c>
-      <c r="F84" t="str" xml:space="preserve">
+      <c r="F95" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /return-books
 2. Observe the table</v>
       </c>
-      <c r="G84" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H84" t="str">
+      <c r="G95" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H95" t="str">
         <v>Only issues with status Issued or Overdue are listed; already-Returned issues are excluded.</v>
       </c>
-      <c r="I84" t="str">
+      <c r="I95" t="str">
         <v>return-books-table</v>
       </c>
-      <c r="J84" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85" xml:space="preserve">
-      <c r="A85" t="str">
+      <c r="J95" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96" xml:space="preserve">
+      <c r="A96" t="str">
         <v>TC-OVERDUE-001</v>
       </c>
-      <c r="B85" t="str">
+      <c r="B96" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C85" t="str">
+      <c r="C96" t="str">
         <v>Overdue table lists only currently overdue issues</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D96" t="str">
         <v>High</v>
       </c>
-      <c r="E85" t="str">
+      <c r="E96" t="str">
         <v>A mix of Issued, Overdue, and Returned issues exist, some past due date.</v>
       </c>
-      <c r="F85" t="str" xml:space="preserve">
+      <c r="F96" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /overdue-books
 2. Observe the table</v>
       </c>
-      <c r="G85" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H85" t="str">
+      <c r="G96" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H96" t="str">
         <v>Only unreturned issues past their due date are listed; on-time and returned issues are excluded.</v>
       </c>
-      <c r="I85" t="str">
+      <c r="I96" t="str">
         <v>overdue-table</v>
       </c>
-      <c r="J85" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86" t="str">
+      <c r="J96" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97" xml:space="preserve">
+      <c r="A97" t="str">
         <v>TC-OVERDUE-002</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B97" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C86" t="str">
+      <c r="C97" t="str">
         <v>Overdue severity is shown correctly for 1-3 days overdue</v>
       </c>
-      <c r="D86" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E86" t="str">
+      <c r="D97" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E97" t="str">
         <v>An issue is 1-3 days past its due date.</v>
       </c>
-      <c r="F86" t="str" xml:space="preserve">
+      <c r="F97" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /overdue-books
 2. Check the severity indicator for that row</v>
       </c>
-      <c r="G86" t="str">
+      <c r="G97" t="str">
         <v>daysOverdue = 2</v>
       </c>
-      <c r="H86" t="str">
+      <c r="H97" t="str">
         <v>Severity is shown as "low" with the corresponding color coding.</v>
       </c>
-      <c r="I86" t="str">
+      <c r="I97" t="str">
         <v>overdue-severity-{id}</v>
       </c>
-      <c r="J86" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K86" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="87" xml:space="preserve">
-      <c r="A87" t="str">
+      <c r="J97" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98" xml:space="preserve">
+      <c r="A98" t="str">
         <v>TC-OVERDUE-003</v>
       </c>
-      <c r="B87" t="str">
+      <c r="B98" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C87" t="str">
+      <c r="C98" t="str">
         <v>Overdue severity is shown correctly for 4-7 days overdue</v>
       </c>
-      <c r="D87" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E87" t="str">
+      <c r="D98" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E98" t="str">
         <v>An issue is 4-7 days past its due date.</v>
       </c>
-      <c r="F87" t="str" xml:space="preserve">
+      <c r="F98" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /overdue-books
 2. Check the severity indicator for that row</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G98" t="str">
         <v>daysOverdue = 6</v>
       </c>
-      <c r="H87" t="str">
+      <c r="H98" t="str">
         <v>Severity is shown as "medium" with the corresponding color coding.</v>
       </c>
-      <c r="I87" t="str">
+      <c r="I98" t="str">
         <v>overdue-severity-{id}</v>
       </c>
-      <c r="J87" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88" xml:space="preserve">
-      <c r="A88" t="str">
+      <c r="J98" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99" xml:space="preserve">
+      <c r="A99" t="str">
         <v>TC-OVERDUE-004</v>
       </c>
-      <c r="B88" t="str">
+      <c r="B99" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C88" t="str">
+      <c r="C99" t="str">
         <v>Overdue severity is shown correctly for more than 7 days overdue</v>
       </c>
-      <c r="D88" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E88" t="str">
+      <c r="D99" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E99" t="str">
         <v>An issue is more than 7 days past its due date.</v>
       </c>
-      <c r="F88" t="str" xml:space="preserve">
+      <c r="F99" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /overdue-books
 2. Check the severity indicator for that row</v>
       </c>
-      <c r="G88" t="str">
+      <c r="G99" t="str">
         <v>daysOverdue = 10</v>
       </c>
-      <c r="H88" t="str">
+      <c r="H99" t="str">
         <v>Severity is shown as "high" with the corresponding color coding.</v>
       </c>
-      <c r="I88" t="str">
+      <c r="I99" t="str">
         <v>overdue-severity-{id}</v>
       </c>
-      <c r="J88" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89" xml:space="preserve">
-      <c r="A89" t="str">
+      <c r="J99" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100" xml:space="preserve">
+      <c r="A100" t="str">
         <v>TC-OVERDUE-005</v>
       </c>
-      <c r="B89" t="str">
+      <c r="B100" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C89" t="str">
+      <c r="C100" t="str">
         <v>"Contact Member" action is available for each overdue row</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D100" t="str">
         <v>Low</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E100" t="str">
         <v>At least one overdue issue exists.</v>
       </c>
-      <c r="F89" t="str" xml:space="preserve">
+      <c r="F100" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /overdue-books
 2. Locate the contact action on a row</v>
       </c>
-      <c r="G89" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H89" t="str">
+      <c r="G100" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H100" t="str">
         <v>A contact-member control is present and identifies the correct member for that row.</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I100" t="str">
         <v>contact-member-{id}</v>
       </c>
-      <c r="J89" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K89" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
+      <c r="J100" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
         <v>TC-OVERDUE-006</v>
       </c>
-      <c r="B90" t="str">
+      <c r="B101" t="str">
         <v>Overdue Books</v>
       </c>
-      <c r="C90" t="str">
+      <c r="C101" t="str">
         <v>Empty state is shown when there are no overdue books</v>
       </c>
-      <c r="D90" t="str">
+      <c r="D101" t="str">
         <v>Low</v>
       </c>
-      <c r="E90" t="str">
+      <c r="E101" t="str">
         <v>No issue records are currently overdue.</v>
       </c>
-      <c r="F90" t="str">
+      <c r="F101" t="str">
         <v>1. Navigate to /overdue-books</v>
       </c>
-      <c r="G90" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H90" t="str">
+      <c r="G101" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H101" t="str">
         <v>An empty-state message is shown instead of the table.</v>
       </c>
-      <c r="I90" t="str">
+      <c r="I101" t="str">
         <v>overdue-table</v>
       </c>
-      <c r="J90" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91" xml:space="preserve">
-      <c r="A91" t="str">
+      <c r="J101" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102" xml:space="preserve">
+      <c r="A102" t="str">
         <v>TC-HIST-001</v>
       </c>
-      <c r="B91" t="str">
+      <c r="B102" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C91" t="str">
+      <c r="C102" t="str">
         <v>Issue history lists all issue records regardless of status</v>
       </c>
-      <c r="D91" t="str">
+      <c r="D102" t="str">
         <v>High</v>
       </c>
-      <c r="E91" t="str">
+      <c r="E102" t="str">
         <v>Issued, Overdue, and Returned issue records exist.</v>
       </c>
-      <c r="F91" t="str" xml:space="preserve">
+      <c r="F102" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /issue-history
 2. Observe the table</v>
       </c>
-      <c r="G91" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H91" t="str">
+      <c r="G102" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H102" t="str">
         <v>All issue records are listed with correct book, member, dates, status, and fine.</v>
       </c>
-      <c r="I91" t="str">
+      <c r="I102" t="str">
         <v>issue-history-table</v>
       </c>
-      <c r="J91" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92" xml:space="preserve">
-      <c r="A92" t="str">
+      <c r="J102" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103" xml:space="preserve">
+      <c r="A103" t="str">
         <v>TC-HIST-002</v>
       </c>
-      <c r="B92" t="str">
+      <c r="B103" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C92" t="str">
+      <c r="C103" t="str">
         <v>Filter issue history by date range</v>
       </c>
-      <c r="D92" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E92" t="str">
+      <c r="D103" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E103" t="str">
         <v>Issue records exist across different dates.</v>
       </c>
-      <c r="F92" t="str" xml:space="preserve">
+      <c r="F103" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Set a From date and To date
 2. Observe the filtered table</v>
       </c>
-      <c r="G92" t="str">
+      <c r="G103" t="str">
         <v>from/to date range</v>
       </c>
-      <c r="H92" t="str">
+      <c r="H103" t="str">
         <v>Only issue records with issue/due dates inside the selected range are shown.</v>
       </c>
-      <c r="I92" t="str">
+      <c r="I103" t="str">
         <v>history-from-date, history-to-date, issue-history-table</v>
       </c>
-      <c r="J92" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K92" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="str">
+      <c r="J103" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
         <v>TC-HIST-003</v>
       </c>
-      <c r="B93" t="str">
+      <c r="B104" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C93" t="str">
+      <c r="C104" t="str">
         <v>Filter issue history by book</v>
       </c>
-      <c r="D93" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E93" t="str">
+      <c r="D104" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E104" t="str">
         <v>Multiple books have issue records.</v>
       </c>
-      <c r="F93" t="str">
+      <c r="F104" t="str">
         <v>1. Select a specific book in the book filter</v>
       </c>
-      <c r="G93" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H93" t="str">
+      <c r="G104" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H104" t="str">
         <v>Only issue records for that book are shown.</v>
       </c>
-      <c r="I93" t="str">
+      <c r="I104" t="str">
         <v>history-book-filter, issue-history-table</v>
       </c>
-      <c r="J93" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K93" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
+      <c r="J104" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>TC-HIST-004</v>
       </c>
-      <c r="B94" t="str">
+      <c r="B105" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C94" t="str">
+      <c r="C105" t="str">
         <v>Filter issue history by member</v>
       </c>
-      <c r="D94" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E94" t="str">
+      <c r="D105" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E105" t="str">
         <v>Multiple members have issue records.</v>
       </c>
-      <c r="F94" t="str">
+      <c r="F105" t="str">
         <v>1. Select a specific member in the member filter</v>
       </c>
-      <c r="G94" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H94" t="str">
+      <c r="G105" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H105" t="str">
         <v>Only issue records for that member are shown.</v>
       </c>
-      <c r="I94" t="str">
+      <c r="I105" t="str">
         <v>history-member-filter, issue-history-table</v>
       </c>
-      <c r="J94" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
+      <c r="J105" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
         <v>TC-HIST-005</v>
       </c>
-      <c r="B95" t="str">
+      <c r="B106" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C95" t="str">
+      <c r="C106" t="str">
         <v>Filter issue history by status</v>
       </c>
-      <c r="D95" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E95" t="str">
+      <c r="D106" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E106" t="str">
         <v>Issued, Overdue, and Returned records exist.</v>
       </c>
-      <c r="F95" t="str">
+      <c r="F106" t="str">
         <v>1. Select "Returned" in the status filter</v>
       </c>
-      <c r="G95" t="str">
+      <c r="G106" t="str">
         <v>status = Returned</v>
       </c>
-      <c r="H95" t="str">
+      <c r="H106" t="str">
         <v>Only Returned issue records are shown.</v>
       </c>
-      <c r="I95" t="str">
+      <c r="I106" t="str">
         <v>history-status-filter, issue-history-table</v>
       </c>
-      <c r="J95" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K95" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
+      <c r="J106" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
         <v>TC-HIST-006</v>
       </c>
-      <c r="B96" t="str">
+      <c r="B107" t="str">
         <v>Issue History</v>
       </c>
-      <c r="C96" t="str">
+      <c r="C107" t="str">
         <v>Pagination works on the issue history table</v>
       </c>
-      <c r="D96" t="str">
+      <c r="D107" t="str">
         <v>Low</v>
       </c>
-      <c r="E96" t="str">
+      <c r="E107" t="str">
         <v>More issue records exist than fit on one page.</v>
       </c>
-      <c r="F96" t="str">
+      <c r="F107" t="str">
         <v>1. Change page size and navigate pages</v>
       </c>
-      <c r="G96" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H96" t="str">
+      <c r="G107" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H107" t="str">
         <v>Rows per page and page navigation behave correctly.</v>
       </c>
-      <c r="I96" t="str">
+      <c r="I107" t="str">
         <v>issue-history-table</v>
       </c>
-      <c r="J96" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K96" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="97" xml:space="preserve">
-      <c r="A97" t="str">
+      <c r="J107" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108" xml:space="preserve">
+      <c r="A108" t="str">
         <v>TC-CAT-001</v>
       </c>
-      <c r="B97" t="str">
+      <c r="B108" t="str">
         <v>Categories</v>
       </c>
-      <c r="C97" t="str">
+      <c r="C108" t="str">
         <v>Categories table lists all categories with book counts</v>
       </c>
-      <c r="D97" t="str">
+      <c r="D108" t="str">
         <v>High</v>
       </c>
-      <c r="E97" t="str">
+      <c r="E108" t="str">
         <v>Categories with assigned books exist.</v>
       </c>
-      <c r="F97" t="str" xml:space="preserve">
+      <c r="F108" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to /categories
 2. Observe the table</v>
       </c>
-      <c r="G97" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H97" t="str">
+      <c r="G108" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H108" t="str">
         <v>Each category row shows its name and the correct count of books assigned to it.</v>
       </c>
-      <c r="I97" t="str">
+      <c r="I108" t="str">
         <v>categories-table</v>
       </c>
-      <c r="J97" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K97" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
+      <c r="J108" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
         <v>TC-CAT-002</v>
       </c>
-      <c r="B98" t="str">
+      <c r="B109" t="str">
         <v>Categories</v>
       </c>
-      <c r="C98" t="str">
+      <c r="C109" t="str">
         <v>Search categories by name</v>
       </c>
-      <c r="D98" t="str">
+      <c r="D109" t="str">
         <v>Low</v>
       </c>
-      <c r="E98" t="str">
+      <c r="E109" t="str">
         <v>Multiple categories exist.</v>
       </c>
-      <c r="F98" t="str">
+      <c r="F109" t="str">
         <v>1. Enter a search term matching one category</v>
       </c>
-      <c r="G98" t="str">
+      <c r="G109" t="str">
         <v>search = "fic"</v>
       </c>
-      <c r="H98" t="str">
+      <c r="H109" t="str">
         <v>Only categories matching the search term (case-insensitive) are shown.</v>
       </c>
-      <c r="I98" t="str">
+      <c r="I109" t="str">
         <v>category-search, categories-table</v>
       </c>
-      <c r="J98" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K98" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="99" xml:space="preserve">
-      <c r="A99" t="str">
+      <c r="J109" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110" xml:space="preserve">
+      <c r="A110" t="str">
         <v>TC-CAT-003</v>
       </c>
-      <c r="B99" t="str">
+      <c r="B110" t="str">
         <v>Categories</v>
       </c>
-      <c r="C99" t="str">
+      <c r="C110" t="str">
         <v>Adding a new category with a valid name succeeds</v>
       </c>
-      <c r="D99" t="str">
+      <c r="D110" t="str">
         <v>High</v>
       </c>
-      <c r="E99" t="str">
+      <c r="E110" t="str">
         <v>User is on /categories.</v>
       </c>
-      <c r="F99" t="str" xml:space="preserve">
+      <c r="F110" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click "Add Category"
 2. Enter a unique name
 3. Click Save</v>
       </c>
-      <c r="G99" t="str">
+      <c r="G110" t="str">
         <v>name = "Poetry"</v>
       </c>
-      <c r="H99" t="str">
+      <c r="H110" t="str">
         <v>Category is added to the table with a book count of 0; success toast shown.</v>
       </c>
-      <c r="I99" t="str">
+      <c r="I110" t="str">
         <v>add-category-button, category-name, save-category-button</v>
       </c>
-      <c r="J99" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K99" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="100" xml:space="preserve">
-      <c r="A100" t="str">
+      <c r="J110" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111" xml:space="preserve">
+      <c r="A111" t="str">
         <v>TC-CAT-004</v>
       </c>
-      <c r="B100" t="str">
+      <c r="B111" t="str">
         <v>Categories</v>
       </c>
-      <c r="C100" t="str">
+      <c r="C111" t="str">
         <v>Adding a category fails when the name is empty</v>
       </c>
-      <c r="D100" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E100" t="str">
+      <c r="D111" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E111" t="str">
         <v>Add Category form is open.</v>
       </c>
-      <c r="F100" t="str" xml:space="preserve">
+      <c r="F111" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Leave the name field empty
 2. Click Save</v>
       </c>
-      <c r="G100" t="str">
+      <c r="G111" t="str">
         <v>name = ""</v>
       </c>
-      <c r="H100" t="str">
+      <c r="H111" t="str">
         <v>Validation error indicates the name is required; category is not added.</v>
       </c>
-      <c r="I100" t="str">
+      <c r="I111" t="str">
         <v>category-name, save-category-button</v>
       </c>
-      <c r="J100" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K100" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="101" xml:space="preserve">
-      <c r="A101" t="str">
+      <c r="J111" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112" xml:space="preserve">
+      <c r="A112" t="str">
         <v>TC-CAT-005</v>
       </c>
-      <c r="B101" t="str">
+      <c r="B112" t="str">
         <v>Categories</v>
       </c>
-      <c r="C101" t="str">
+      <c r="C112" t="str">
         <v>Adding a category fails with a duplicate name (case-insensitive)</v>
       </c>
-      <c r="D101" t="str">
+      <c r="D112" t="str">
         <v>High</v>
       </c>
-      <c r="E101" t="str">
+      <c r="E112" t="str">
         <v>A category named "Fiction" already exists.</v>
       </c>
-      <c r="F101" t="str" xml:space="preserve">
+      <c r="F112" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter "fiction" (different case)
 2. Click Save</v>
       </c>
-      <c r="G101" t="str">
+      <c r="G112" t="str">
         <v>name = "fiction"</v>
       </c>
-      <c r="H101" t="str">
+      <c r="H112" t="str">
         <v>Validation error indicates a category with this name already exists; category is not added.</v>
       </c>
-      <c r="I101" t="str">
+      <c r="I112" t="str">
         <v>category-name, save-category-button</v>
       </c>
-      <c r="J101" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K101" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="102" xml:space="preserve">
-      <c r="A102" t="str">
+      <c r="J112" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113" xml:space="preserve">
+      <c r="A113" t="str">
         <v>TC-CAT-006</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B113" t="str">
         <v>Categories</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C113" t="str">
         <v>Editing a category renames it</v>
       </c>
-      <c r="D102" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E102" t="str">
+      <c r="D113" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E113" t="str">
         <v>A category exists that is not currently in use, or renaming does not conflict.</v>
       </c>
-      <c r="F102" t="str" xml:space="preserve">
+      <c r="F113" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Edit on a category
 2. Change the name
 3. Click Save</v>
       </c>
-      <c r="G102" t="str">
+      <c r="G113" t="str">
         <v>new unique name</v>
       </c>
-      <c r="H102" t="str">
+      <c r="H113" t="str">
         <v>Category name updates in the table and in storage; books referencing it (if any) still resolve correctly.</v>
       </c>
-      <c r="I102" t="str">
+      <c r="I113" t="str">
         <v>edit-category-{id}, category-name, save-category-button</v>
       </c>
-      <c r="J102" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="103" xml:space="preserve">
-      <c r="A103" t="str">
+      <c r="J113" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114" xml:space="preserve">
+      <c r="A114" t="str">
         <v>TC-CAT-007</v>
       </c>
-      <c r="B103" t="str">
+      <c r="B114" t="str">
         <v>Categories</v>
       </c>
-      <c r="C103" t="str">
+      <c r="C114" t="str">
         <v>Deleting an unused category succeeds</v>
       </c>
-      <c r="D103" t="str">
+      <c r="D114" t="str">
         <v>High</v>
       </c>
-      <c r="E103" t="str">
+      <c r="E114" t="str">
         <v>A category exists with zero books assigned.</v>
       </c>
-      <c r="F103" t="str" xml:space="preserve">
+      <c r="F114" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Delete on that category
 2. Confirm</v>
       </c>
-      <c r="G103" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H103" t="str">
+      <c r="G114" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H114" t="str">
         <v>Category is removed from the table and storage.</v>
       </c>
-      <c r="I103" t="str">
+      <c r="I114" t="str">
         <v>delete-category-{id}</v>
       </c>
-      <c r="J103" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K103" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="104" xml:space="preserve">
-      <c r="A104" t="str">
+      <c r="J114" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115" xml:space="preserve">
+      <c r="A115" t="str">
         <v>TC-CAT-008</v>
       </c>
-      <c r="B104" t="str">
+      <c r="B115" t="str">
         <v>Categories</v>
       </c>
-      <c r="C104" t="str">
+      <c r="C115" t="str">
         <v>Deleting a category with assigned books is blocked</v>
       </c>
-      <c r="D104" t="str">
+      <c r="D115" t="str">
         <v>High</v>
       </c>
-      <c r="E104" t="str">
+      <c r="E115" t="str">
         <v>A category has one or more books currently assigned to it.</v>
       </c>
-      <c r="F104" t="str" xml:space="preserve">
+      <c r="F115" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Delete on that category
 2. Attempt to confirm</v>
       </c>
-      <c r="G104" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H104" t="str">
+      <c r="G115" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H115" t="str">
         <v>Deletion is blocked with an error message indicating the category still has books assigned; category is not removed.</v>
       </c>
-      <c r="I104" t="str">
+      <c r="I115" t="str">
         <v>delete-category-{id}, toast-error</v>
       </c>
-      <c r="J104" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K104" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
+      <c r="J115" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116" xml:space="preserve">
+      <c r="A116" t="str">
+        <v>TC-CAT-009</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Categories</v>
+      </c>
+      <c r="C116" t="str">
+        <v>"Books Assigned" counts distinct book titles, not total copies</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E116" t="str">
+        <v>A category has zero books assigned.</v>
+      </c>
+      <c r="F116" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Note the category's "Books Assigned" count
+2. Add one new book to that category with Number of Copies &gt; 1 (e.g. 5)
+3. Return to Categories</v>
+      </c>
+      <c r="G116" t="str">
+        <v>New book with totalCopies = 5, category = the noted category</v>
+      </c>
+      <c r="H116" t="str">
+        <v>"Books Assigned" increases by exactly 1 (one title), not by the number of copies (5).</v>
+      </c>
+      <c r="I116" t="str">
+        <v>categories-table, add-book-button, book-total-copies</v>
+      </c>
+      <c r="J116" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117" xml:space="preserve">
+      <c r="A117" t="str">
+        <v>TC-CAT-010</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Categories</v>
+      </c>
+      <c r="C117" t="str">
+        <v>Increasing an existing book's copy count does not change its category's "Books Assigned" count</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E117" t="str">
+        <v>An existing book belongs to a known category.</v>
+      </c>
+      <c r="F117" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Note the category's "Books Assigned" count
+2. Edit that book, increasing Number of Copies
+3. Save
+4. Return to Categories</v>
+      </c>
+      <c r="G117" t="str">
+        <v>e.g. totalCopies 3 -&gt; 10</v>
+      </c>
+      <c r="H117" t="str">
+        <v>"Books Assigned" for that category is unchanged (still counts 1 title, regardless of copy count).</v>
+      </c>
+      <c r="I117" t="str">
+        <v>categories-table, edit-book-{id}, book-total-copies</v>
+      </c>
+      <c r="J117" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
         <v>TC-PROF-001</v>
       </c>
-      <c r="B105" t="str">
+      <c r="B118" t="str">
         <v>Profile</v>
       </c>
-      <c r="C105" t="str">
+      <c r="C118" t="str">
         <v>Profile page displays the current user's information</v>
       </c>
-      <c r="D105" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E105" t="str">
+      <c r="D118" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E118" t="str">
         <v>User is logged in.</v>
       </c>
-      <c r="F105" t="str">
+      <c r="F118" t="str">
         <v>1. Navigate to /profile</v>
       </c>
-      <c r="G105" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H105" t="str">
+      <c r="G118" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H118" t="str">
         <v>Name, email, phone, address, and role are displayed and match the logged-in user.</v>
       </c>
-      <c r="I105" t="str">
+      <c r="I118" t="str">
         <v>profile-form</v>
       </c>
-      <c r="J105" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K105" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="106" xml:space="preserve">
-      <c r="A106" t="str">
+      <c r="J118" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119" xml:space="preserve">
+      <c r="A119" t="str">
         <v>TC-PROF-002</v>
       </c>
-      <c r="B106" t="str">
+      <c r="B119" t="str">
         <v>Profile</v>
       </c>
-      <c r="C106" t="str">
+      <c r="C119" t="str">
         <v>Editing the profile updates name/phone/address successfully</v>
       </c>
-      <c r="D106" t="str">
+      <c r="D119" t="str">
         <v>High</v>
       </c>
-      <c r="E106" t="str">
+      <c r="E119" t="str">
         <v>User is on /profile.</v>
       </c>
-      <c r="F106" t="str" xml:space="preserve">
+      <c r="F119" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Click Edit Profile
 2. Change name, phone, and address
 3. Click Save</v>
       </c>
-      <c r="G106" t="str">
+      <c r="G119" t="str">
         <v>New valid name/phone/address</v>
       </c>
-      <c r="H106" t="str">
+      <c r="H119" t="str">
         <v>Profile updates and persists; success toast shown; sidebar/topbar reflect the new name.</v>
       </c>
-      <c r="I106" t="str">
+      <c r="I119" t="str">
         <v>edit-profile-button, profile-form</v>
       </c>
-      <c r="J106" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K106" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="107" xml:space="preserve">
-      <c r="A107" t="str">
+      <c r="J119" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120" xml:space="preserve">
+      <c r="A120" t="str">
         <v>TC-PROF-003</v>
       </c>
-      <c r="B107" t="str">
+      <c r="B120" t="str">
         <v>Profile</v>
       </c>
-      <c r="C107" t="str">
+      <c r="C120" t="str">
         <v>Editing the profile fails with an invalid email or phone</v>
       </c>
-      <c r="D107" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E107" t="str">
+      <c r="D120" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E120" t="str">
         <v>Edit Profile form is open.</v>
       </c>
-      <c r="F107" t="str" xml:space="preserve">
+      <c r="F120" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter an invalid email or phone
 2. Click Save</v>
       </c>
-      <c r="G107" t="str">
+      <c r="G120" t="str">
         <v>email = "not-an-email" or phone = "123"</v>
       </c>
-      <c r="H107" t="str">
+      <c r="H120" t="str">
         <v>Validation error is shown; profile is not updated.</v>
       </c>
-      <c r="I107" t="str">
+      <c r="I120" t="str">
         <v>profile-form</v>
       </c>
-      <c r="J107" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K107" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="108" xml:space="preserve">
-      <c r="A108" t="str">
+      <c r="J120" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121" xml:space="preserve">
+      <c r="A121" t="str">
         <v>TC-PROF-004</v>
       </c>
-      <c r="B108" t="str">
+      <c r="B121" t="str">
         <v>Profile</v>
       </c>
-      <c r="C108" t="str">
+      <c r="C121" t="str">
         <v>Changing the password fails when a rule is not met</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D121" t="str">
         <v>High</v>
       </c>
-      <c r="E108" t="str">
+      <c r="E121" t="str">
         <v>User is on /profile with the change-password form open.</v>
       </c>
-      <c r="F108" t="str" xml:space="preserve">
+      <c r="F121" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter a new password missing a required rule (e.g. no special character)
 2. Submit</v>
       </c>
-      <c r="G108" t="str">
+      <c r="G121" t="str">
         <v>newPassword = "Password1"</v>
       </c>
-      <c r="H108" t="str">
+      <c r="H121" t="str">
         <v>Validation error is shown identifying the unmet rule(s); password is not changed.</v>
       </c>
-      <c r="I108" t="str">
+      <c r="I121" t="str">
         <v>change-password-button, change-password-form, password-rules</v>
       </c>
-      <c r="J108" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K108" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="109" xml:space="preserve">
-      <c r="A109" t="str">
+      <c r="J121" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122" xml:space="preserve">
+      <c r="A122" t="str">
         <v>TC-PROF-005</v>
       </c>
-      <c r="B109" t="str">
+      <c r="B122" t="str">
         <v>Profile</v>
       </c>
-      <c r="C109" t="str">
+      <c r="C122" t="str">
         <v>Changing the password fails when confirmation does not match</v>
       </c>
-      <c r="D109" t="str">
+      <c r="D122" t="str">
         <v>High</v>
       </c>
-      <c r="E109" t="str">
+      <c r="E122" t="str">
         <v>Change-password form is open with a valid new password entered.</v>
       </c>
-      <c r="F109" t="str" xml:space="preserve">
+      <c r="F122" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter a different value in the confirm-password field
 2. Submit</v>
       </c>
-      <c r="G109" t="str">
+      <c r="G122" t="str">
         <v>newPassword = "Admin@1234", confirm = "Admin@1235"</v>
       </c>
-      <c r="H109" t="str">
+      <c r="H122" t="str">
         <v>Validation error indicates the passwords do not match; password is not changed.</v>
       </c>
-      <c r="I109" t="str">
+      <c r="I122" t="str">
         <v>change-password-form</v>
       </c>
-      <c r="J109" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K109" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="110" xml:space="preserve">
-      <c r="A110" t="str">
+      <c r="J122" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123" xml:space="preserve">
+      <c r="A123" t="str">
         <v>TC-PROF-006</v>
       </c>
-      <c r="B110" t="str">
+      <c r="B123" t="str">
         <v>Profile</v>
       </c>
-      <c r="C110" t="str">
+      <c r="C123" t="str">
         <v>Changing the password succeeds with a valid, matching new password</v>
       </c>
-      <c r="D110" t="str">
+      <c r="D123" t="str">
         <v>High</v>
       </c>
-      <c r="E110" t="str">
+      <c r="E123" t="str">
         <v>Change-password form is open.</v>
       </c>
-      <c r="F110" t="str" xml:space="preserve">
+      <c r="F123" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Enter current password
 2. Enter a valid new password meeting all rules
 3. Confirm it matches
 4. Submit</v>
       </c>
-      <c r="G110" t="str">
+      <c r="G123" t="str">
         <v>current = Admin@123, new = "NewPass@123", confirm = "NewPass@123"</v>
       </c>
-      <c r="H110" t="str">
+      <c r="H123" t="str">
         <v>Password is updated; success toast shown; user can log in with the new password afterward.</v>
       </c>
-      <c r="I110" t="str">
+      <c r="I123" t="str">
         <v>change-password-form, password-rules</v>
       </c>
-      <c r="J110" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K110" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="str">
+      <c r="J123" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
         <v>TC-PROF-007</v>
       </c>
-      <c r="B111" t="str">
+      <c r="B124" t="str">
         <v>Profile</v>
       </c>
-      <c r="C111" t="str">
+      <c r="C124" t="str">
         <v>Password rule checklist updates live as the user types</v>
       </c>
-      <c r="D111" t="str">
+      <c r="D124" t="str">
         <v>Low</v>
       </c>
-      <c r="E111" t="str">
+      <c r="E124" t="str">
         <v>Change-password form is open.</v>
       </c>
-      <c r="F111" t="str">
+      <c r="F124" t="str">
         <v>1. Type a new password character by character, satisfying rules progressively</v>
       </c>
-      <c r="G111" t="str">
+      <c r="G124" t="str">
         <v>e.g. type "Abcdef1!"</v>
       </c>
-      <c r="H111" t="str">
+      <c r="H124" t="str">
         <v>Each rule (length, uppercase, lowercase, number, special character) toggles to satisfied in real time.</v>
       </c>
-      <c r="I111" t="str">
+      <c r="I124" t="str">
         <v>password-rules</v>
       </c>
-      <c r="J111" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K111" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="112" xml:space="preserve">
-      <c r="A112" t="str">
+      <c r="J124" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125" xml:space="preserve">
+      <c r="A125" t="str">
         <v>TC-PROF-008</v>
       </c>
-      <c r="B112" t="str">
+      <c r="B125" t="str">
         <v>Profile</v>
       </c>
-      <c r="C112" t="str">
+      <c r="C125" t="str">
         <v>Reset Demo Data restores the original seeded dataset</v>
       </c>
-      <c r="D112" t="str">
-        <v>Medium</v>
-      </c>
-      <c r="E112" t="str">
+      <c r="D125" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E125" t="str">
         <v>Existing data has been modified (e.g. a book was deleted).</v>
       </c>
-      <c r="F112" t="str" xml:space="preserve">
+      <c r="F125" t="str" xml:space="preserve">
         <v xml:space="preserve">1. Navigate to Profile &gt; Test Environment Settings
 2. Click "Reset Demo Data"
 3. Confirm</v>
       </c>
-      <c r="G112" t="str">
-        <v>N/A</v>
-      </c>
-      <c r="H112" t="str">
+      <c r="G125" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H125" t="str">
         <v>All books/members/issues/categories/activity are wiped and re-seeded to the original 30/20/20/9 dataset.</v>
       </c>
-      <c r="I112" t="str">
+      <c r="I125" t="str">
         <v>reset-demo-data-button, reset-demo-data-dialog</v>
       </c>
-      <c r="J112" t="str">
-        <v>Not Automated</v>
-      </c>
-      <c r="K112" t="str">
+      <c r="J125" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>TC-ACCT-001</v>
+      </c>
+      <c r="B126" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C126" t="str">
+        <v>My Account displays the logged-in member's profile summary</v>
+      </c>
+      <c r="D126" t="str">
+        <v>High</v>
+      </c>
+      <c r="E126" t="str">
+        <v>User is logged in with role Member.</v>
+      </c>
+      <c r="F126" t="str">
+        <v>1. Navigate to /my-account</v>
+      </c>
+      <c r="G126" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H126" t="str">
+        <v>Name, membership type, status, join date, email, phone, address, and membership expiry are all displayed and match the member's own record.</v>
+      </c>
+      <c r="I126" t="str">
+        <v>my-account-page, my-account-profile, my-account-name, my-account-status</v>
+      </c>
+      <c r="J126" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127" xml:space="preserve">
+      <c r="A127" t="str">
+        <v>TC-ACCT-002</v>
+      </c>
+      <c r="B127" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C127" t="str">
+        <v>Stat tiles show correct current-loan, overdue, fine, and membership values</v>
+      </c>
+      <c r="D127" t="str">
+        <v>High</v>
+      </c>
+      <c r="E127" t="str">
+        <v>The member has a mix of current loans (including at least one overdue) and returned loans.</v>
+      </c>
+      <c r="F127" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /my-account
+2. Read the four stat tiles</v>
+      </c>
+      <c r="G127" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H127" t="str">
+        <v>Books Borrowed = count of unreturned issues; Overdue = count of unreturned issues past due date; Fine Due = live sum of overdue fines (₹10/day); Membership = the member's membershipType.</v>
+      </c>
+      <c r="I127" t="str">
+        <v>stat-current-loans, stat-overdue-loans, stat-outstanding-fine, stat-membership-type</v>
+      </c>
+      <c r="J127" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128" xml:space="preserve">
+      <c r="A128" t="str">
+        <v>TC-ACCT-003</v>
+      </c>
+      <c r="B128" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C128" t="str">
+        <v>Currently Borrowed table lists only unreturned issues for this member</v>
+      </c>
+      <c r="D128" t="str">
+        <v>High</v>
+      </c>
+      <c r="E128" t="str">
+        <v>The member has both active and returned issues, and other members have their own unrelated issues.</v>
+      </c>
+      <c r="F128" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /my-account
+2. Observe the Currently Borrowed table</v>
+      </c>
+      <c r="G128" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H128" t="str">
+        <v>Only this member's unreturned (Issued/Overdue) books are listed with book title, issue date, due date, status, and live fine-if-returned-today; other members' issues never appear.</v>
+      </c>
+      <c r="I128" t="str">
+        <v>current-loans-table, current-loan-row-{id}</v>
+      </c>
+      <c r="J128" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>TC-ACCT-004</v>
+      </c>
+      <c r="B129" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C129" t="str">
+        <v>Currently Borrowed shows an empty state when nothing is on loan</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E129" t="str">
+        <v>The member has zero unreturned issues.</v>
+      </c>
+      <c r="F129" t="str">
+        <v>1. Navigate to /my-account</v>
+      </c>
+      <c r="G129" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H129" t="str">
+        <v>An empty-state message ("No books currently borrowed") is shown instead of the table.</v>
+      </c>
+      <c r="I129" t="str">
+        <v>current-loans-empty</v>
+      </c>
+      <c r="J129" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130" xml:space="preserve">
+      <c r="A130" t="str">
+        <v>TC-ACCT-005</v>
+      </c>
+      <c r="B130" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C130" t="str">
+        <v>Borrowing History lists only this member's returned books</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="E130" t="str">
+        <v>The member has at least one returned issue.</v>
+      </c>
+      <c r="F130" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /my-account
+2. Observe the Borrowing History table</v>
+      </c>
+      <c r="G130" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H130" t="str">
+        <v>Each returned issue shows book title, issue date, return date, and the fine that was actually paid (stored value, not recalculated).</v>
+      </c>
+      <c r="I130" t="str">
+        <v>past-loans-table, past-loan-row-{id}</v>
+      </c>
+      <c r="J130" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>TC-ACCT-006</v>
+      </c>
+      <c r="B131" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C131" t="str">
+        <v>Borrowing History shows an empty state when nothing has been returned yet</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E131" t="str">
+        <v>The member has zero returned issues.</v>
+      </c>
+      <c r="F131" t="str">
+        <v>1. Navigate to /my-account</v>
+      </c>
+      <c r="G131" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H131" t="str">
+        <v>An empty-state message ("No returned books yet") is shown instead of the table.</v>
+      </c>
+      <c r="I131" t="str">
+        <v>past-loans-empty</v>
+      </c>
+      <c r="J131" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>TC-ACCT-007</v>
+      </c>
+      <c r="B132" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C132" t="str">
+        <v>A Member with no linked member record sees a graceful fallback</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E132" t="str">
+        <v>An authenticated user's account has no matching Member record (edge case / data-integrity check).</v>
+      </c>
+      <c r="F132" t="str">
+        <v>1. Navigate to /my-account</v>
+      </c>
+      <c r="G132" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H132" t="str">
+        <v>A "No linked member record" message is shown instead of a crash or blank page.</v>
+      </c>
+      <c r="I132" t="str">
+        <v>my-account-unavailable</v>
+      </c>
+      <c r="J132" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>TC-ACCT-008</v>
+      </c>
+      <c r="B133" t="str">
+        <v>My Account (Member Self-Service)</v>
+      </c>
+      <c r="C133" t="str">
+        <v>Sidebar shows "My Account" as the active link while on this page</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Low</v>
+      </c>
+      <c r="E133" t="str">
+        <v>User is logged in as Member and on /my-account.</v>
+      </c>
+      <c r="F133" t="str">
+        <v>1. Observe the sidebar</v>
+      </c>
+      <c r="G133" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="H133" t="str">
+        <v>The "My Account" link is visually marked active; "Profile" is not.</v>
+      </c>
+      <c r="I133" t="str">
+        <v>nav-my-account</v>
+      </c>
+      <c r="J133" t="str">
+        <v>Not Automated</v>
+      </c>
+      <c r="K133" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K112"/>
+  <autoFilter ref="A1:K133"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K133"/>
   </ignoredErrors>
 </worksheet>
 </file>